--- a/reports/Angola_3.2_imports_products_HS-AG6-2003-2024_top_25.xlsx
+++ b/reports/Angola_3.2_imports_products_HS-AG6-2003-2024_top_25.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2211" uniqueCount="221">
   <si>
     <t>refYear</t>
   </si>
@@ -319,7 +319,7 @@
     <t>730441</t>
   </si>
   <si>
-    <t>100590</t>
+    <t>854449</t>
   </si>
   <si>
     <t>Floating or submersible drilling or production platforms</t>
@@ -661,13 +661,10 @@
     <t>Steel, stainless; cold-drawn or cold-rolled (cold-reduced), tubes and pipes of circular cross-section</t>
   </si>
   <si>
-    <t>Cereals; maize (corn), other than seed</t>
+    <t>Insulated electric conductors; for a voltage not exceeding 1000 volts, not fitted with connectors</t>
   </si>
   <si>
     <t>H2</t>
-  </si>
-  <si>
-    <t>H1</t>
   </si>
   <si>
     <t>H3</t>
@@ -2043,7 +2040,7 @@
         <v>0.05817432455399191</v>
       </c>
       <c r="H29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I29">
         <v>6</v>
@@ -2107,10 +2104,10 @@
         <v>108</v>
       </c>
       <c r="F31">
-        <v>79799822.82100001</v>
+        <v>79799822.82099999</v>
       </c>
       <c r="G31">
-        <v>0.01207674315238515</v>
+        <v>0.01207674315238514</v>
       </c>
       <c r="H31" t="s">
         <v>216</v>
@@ -2142,10 +2139,10 @@
         <v>121</v>
       </c>
       <c r="F32">
-        <v>77837732.99499999</v>
+        <v>77837732.995</v>
       </c>
       <c r="G32">
-        <v>0.01177980446213689</v>
+        <v>0.0117798044621369</v>
       </c>
       <c r="H32" t="s">
         <v>216</v>
@@ -2288,7 +2285,7 @@
         <v>0.007792768652099354</v>
       </c>
       <c r="H36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I36">
         <v>6</v>
@@ -2390,10 +2387,10 @@
         <v>44588722.767</v>
       </c>
       <c r="G39">
-        <v>0.006747966766265296</v>
+        <v>0.006747966766265294</v>
       </c>
       <c r="H39" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I39">
         <v>6</v>
@@ -2498,7 +2495,7 @@
         <v>0.005373236887324196</v>
       </c>
       <c r="H42" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I42">
         <v>6</v>
@@ -2533,7 +2530,7 @@
         <v>0.005358940250403297</v>
       </c>
       <c r="H43" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I43">
         <v>6</v>
@@ -2673,7 +2670,7 @@
         <v>0.004778397590283826</v>
       </c>
       <c r="H47" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I47">
         <v>6</v>
@@ -2813,7 +2810,7 @@
         <v>0.004344962715574392</v>
       </c>
       <c r="H51" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I51">
         <v>6</v>
@@ -4598,7 +4595,7 @@
         <v>0.04260869624756772</v>
       </c>
       <c r="H102" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I102">
         <v>6</v>
@@ -4633,7 +4630,7 @@
         <v>0.02679327357155867</v>
       </c>
       <c r="H103" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I103">
         <v>6</v>
@@ -4668,7 +4665,7 @@
         <v>0.01423723800750681</v>
       </c>
       <c r="H104" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I104">
         <v>6</v>
@@ -4703,7 +4700,7 @@
         <v>0.01290095966033775</v>
       </c>
       <c r="H105" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I105">
         <v>6</v>
@@ -4738,7 +4735,7 @@
         <v>0.01257497346546642</v>
       </c>
       <c r="H106" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I106">
         <v>6</v>
@@ -4773,7 +4770,7 @@
         <v>0.01224292155915192</v>
       </c>
       <c r="H107" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I107">
         <v>6</v>
@@ -4808,7 +4805,7 @@
         <v>0.01192939985138486</v>
       </c>
       <c r="H108" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I108">
         <v>6</v>
@@ -4878,7 +4875,7 @@
         <v>0.01124608586749488</v>
       </c>
       <c r="H110" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I110">
         <v>6</v>
@@ -4913,7 +4910,7 @@
         <v>0.01068762635440646</v>
       </c>
       <c r="H111" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I111">
         <v>6</v>
@@ -4948,7 +4945,7 @@
         <v>0.01052053733590091</v>
       </c>
       <c r="H112" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I112">
         <v>6</v>
@@ -4983,7 +4980,7 @@
         <v>0.009846655705874114</v>
       </c>
       <c r="H113" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I113">
         <v>6</v>
@@ -5018,7 +5015,7 @@
         <v>0.009603228418466237</v>
       </c>
       <c r="H114" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I114">
         <v>6</v>
@@ -5053,7 +5050,7 @@
         <v>0.009582429081452515</v>
       </c>
       <c r="H115" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I115">
         <v>6</v>
@@ -5088,7 +5085,7 @@
         <v>0.009340145358855053</v>
       </c>
       <c r="H116" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I116">
         <v>6</v>
@@ -5123,7 +5120,7 @@
         <v>0.009335652700964914</v>
       </c>
       <c r="H117" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I117">
         <v>6</v>
@@ -5158,7 +5155,7 @@
         <v>0.009308127742491632</v>
       </c>
       <c r="H118" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I118">
         <v>6</v>
@@ -5193,7 +5190,7 @@
         <v>0.009135832030473164</v>
       </c>
       <c r="H119" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I119">
         <v>6</v>
@@ -5228,7 +5225,7 @@
         <v>0.008434891763949796</v>
       </c>
       <c r="H120" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I120">
         <v>6</v>
@@ -5263,7 +5260,7 @@
         <v>0.008363987903731565</v>
       </c>
       <c r="H121" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I121">
         <v>6</v>
@@ -5298,7 +5295,7 @@
         <v>0.008238896680117166</v>
       </c>
       <c r="H122" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I122">
         <v>6</v>
@@ -5333,7 +5330,7 @@
         <v>0.007965729177521193</v>
       </c>
       <c r="H123" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I123">
         <v>6</v>
@@ -5368,7 +5365,7 @@
         <v>0.007067727831054964</v>
       </c>
       <c r="H124" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I124">
         <v>6</v>
@@ -5403,7 +5400,7 @@
         <v>0.007065341566541167</v>
       </c>
       <c r="H125" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I125">
         <v>6</v>
@@ -5438,7 +5435,7 @@
         <v>0.006564785986841916</v>
       </c>
       <c r="H126" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I126">
         <v>6</v>
@@ -5473,7 +5470,7 @@
         <v>0.04772350505532007</v>
       </c>
       <c r="H127" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I127">
         <v>6</v>
@@ -5508,7 +5505,7 @@
         <v>0.02909819717669814</v>
       </c>
       <c r="H128" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I128">
         <v>6</v>
@@ -5543,7 +5540,7 @@
         <v>0.02370632116216123</v>
       </c>
       <c r="H129" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I129">
         <v>6</v>
@@ -5578,7 +5575,7 @@
         <v>0.01855869270247093</v>
       </c>
       <c r="H130" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I130">
         <v>6</v>
@@ -5613,7 +5610,7 @@
         <v>0.01702934339540132</v>
       </c>
       <c r="H131" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I131">
         <v>6</v>
@@ -5648,7 +5645,7 @@
         <v>0.01360087809345388</v>
       </c>
       <c r="H132" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I132">
         <v>6</v>
@@ -5683,7 +5680,7 @@
         <v>0.01315517832842572</v>
       </c>
       <c r="H133" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I133">
         <v>6</v>
@@ -5718,7 +5715,7 @@
         <v>0.01283972246534929</v>
       </c>
       <c r="H134" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I134">
         <v>6</v>
@@ -5753,7 +5750,7 @@
         <v>0.01250042810018247</v>
       </c>
       <c r="H135" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I135">
         <v>6</v>
@@ -5788,7 +5785,7 @@
         <v>0.01181635658602855</v>
       </c>
       <c r="H136" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I136">
         <v>6</v>
@@ -5823,7 +5820,7 @@
         <v>0.01160545143832855</v>
       </c>
       <c r="H137" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I137">
         <v>6</v>
@@ -5858,7 +5855,7 @@
         <v>0.01139183375282201</v>
       </c>
       <c r="H138" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I138">
         <v>6</v>
@@ -5893,7 +5890,7 @@
         <v>0.01008886129549938</v>
       </c>
       <c r="H139" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I139">
         <v>6</v>
@@ -5928,7 +5925,7 @@
         <v>0.008966611487120425</v>
       </c>
       <c r="H140" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I140">
         <v>6</v>
@@ -5963,7 +5960,7 @@
         <v>0.008863631867015442</v>
       </c>
       <c r="H141" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I141">
         <v>6</v>
@@ -5998,7 +5995,7 @@
         <v>0.008588115304119081</v>
       </c>
       <c r="H142" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I142">
         <v>6</v>
@@ -6033,7 +6030,7 @@
         <v>0.008282942079787498</v>
       </c>
       <c r="H143" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I143">
         <v>6</v>
@@ -6068,7 +6065,7 @@
         <v>0.00816103176321337</v>
       </c>
       <c r="H144" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I144">
         <v>6</v>
@@ -6103,7 +6100,7 @@
         <v>0.008059274978353221</v>
       </c>
       <c r="H145" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I145">
         <v>6</v>
@@ -6138,7 +6135,7 @@
         <v>0.008027534026981684</v>
       </c>
       <c r="H146" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I146">
         <v>6</v>
@@ -6173,7 +6170,7 @@
         <v>0.007548404538244395</v>
       </c>
       <c r="H147" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I147">
         <v>6</v>
@@ -6208,7 +6205,7 @@
         <v>0.006993901519265522</v>
       </c>
       <c r="H148" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I148">
         <v>6</v>
@@ -6243,7 +6240,7 @@
         <v>0.006893712445645358</v>
       </c>
       <c r="H149" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I149">
         <v>6</v>
@@ -6278,7 +6275,7 @@
         <v>0.006627783406386734</v>
       </c>
       <c r="H150" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I150">
         <v>6</v>
@@ -6313,7 +6310,7 @@
         <v>0.006402438031677793</v>
       </c>
       <c r="H151" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I151">
         <v>6</v>
@@ -6348,7 +6345,7 @@
         <v>0.03532137069272036</v>
       </c>
       <c r="H152" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I152">
         <v>6</v>
@@ -6418,7 +6415,7 @@
         <v>0.02529635692632756</v>
       </c>
       <c r="H154" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I154">
         <v>6</v>
@@ -6453,7 +6450,7 @@
         <v>0.01727465389395887</v>
       </c>
       <c r="H155" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I155">
         <v>6</v>
@@ -6488,7 +6485,7 @@
         <v>0.01709924738953741</v>
       </c>
       <c r="H156" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I156">
         <v>6</v>
@@ -6523,7 +6520,7 @@
         <v>0.01179576962097835</v>
       </c>
       <c r="H157" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I157">
         <v>6</v>
@@ -6558,7 +6555,7 @@
         <v>0.01162120645390373</v>
       </c>
       <c r="H158" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I158">
         <v>6</v>
@@ -6593,7 +6590,7 @@
         <v>0.01118251244340525</v>
       </c>
       <c r="H159" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I159">
         <v>6</v>
@@ -6628,7 +6625,7 @@
         <v>0.01055786754841576</v>
       </c>
       <c r="H160" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I160">
         <v>6</v>
@@ -6663,7 +6660,7 @@
         <v>0.01033281066499982</v>
       </c>
       <c r="H161" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I161">
         <v>6</v>
@@ -6698,7 +6695,7 @@
         <v>0.00926973519810478</v>
       </c>
       <c r="H162" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I162">
         <v>6</v>
@@ -6733,7 +6730,7 @@
         <v>0.00923329855549257</v>
       </c>
       <c r="H163" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I163">
         <v>6</v>
@@ -6768,7 +6765,7 @@
         <v>0.008974355902400293</v>
       </c>
       <c r="H164" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I164">
         <v>6</v>
@@ -6803,7 +6800,7 @@
         <v>0.008898810235918115</v>
       </c>
       <c r="H165" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I165">
         <v>6</v>
@@ -6838,7 +6835,7 @@
         <v>0.008843394631144034</v>
       </c>
       <c r="H166" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I166">
         <v>6</v>
@@ -6873,7 +6870,7 @@
         <v>0.007629129679109214</v>
       </c>
       <c r="H167" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I167">
         <v>6</v>
@@ -6908,7 +6905,7 @@
         <v>0.007540347788375371</v>
       </c>
       <c r="H168" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I168">
         <v>6</v>
@@ -6943,7 +6940,7 @@
         <v>0.007421804897949172</v>
       </c>
       <c r="H169" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I169">
         <v>6</v>
@@ -6978,7 +6975,7 @@
         <v>0.007421553795194414</v>
       </c>
       <c r="H170" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I170">
         <v>6</v>
@@ -7013,7 +7010,7 @@
         <v>0.006611895153951131</v>
       </c>
       <c r="H171" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I171">
         <v>6</v>
@@ -7048,7 +7045,7 @@
         <v>0.006167036027414811</v>
       </c>
       <c r="H172" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I172">
         <v>6</v>
@@ -7083,7 +7080,7 @@
         <v>0.006111096376387386</v>
       </c>
       <c r="H173" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I173">
         <v>6</v>
@@ -7118,7 +7115,7 @@
         <v>0.006091986980190738</v>
       </c>
       <c r="H174" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I174">
         <v>6</v>
@@ -7153,7 +7150,7 @@
         <v>0.006016525960565763</v>
       </c>
       <c r="H175" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I175">
         <v>6</v>
@@ -7188,7 +7185,7 @@
         <v>0.00596080534532677</v>
       </c>
       <c r="H176" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I176">
         <v>6</v>
@@ -7223,7 +7220,7 @@
         <v>0.03828896560061605</v>
       </c>
       <c r="H177" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I177">
         <v>6</v>
@@ -7293,7 +7290,7 @@
         <v>0.02676158294227223</v>
       </c>
       <c r="H179" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I179">
         <v>6</v>
@@ -7328,7 +7325,7 @@
         <v>0.01681928341729312</v>
       </c>
       <c r="H180" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I180">
         <v>6</v>
@@ -7398,7 +7395,7 @@
         <v>0.01604351779528214</v>
       </c>
       <c r="H182" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I182">
         <v>6</v>
@@ -7433,7 +7430,7 @@
         <v>0.01220496043587766</v>
       </c>
       <c r="H183" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I183">
         <v>6</v>
@@ -7468,7 +7465,7 @@
         <v>0.01200690669446202</v>
       </c>
       <c r="H184" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I184">
         <v>6</v>
@@ -7503,7 +7500,7 @@
         <v>0.01132295800084158</v>
       </c>
       <c r="H185" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I185">
         <v>6</v>
@@ -7538,7 +7535,7 @@
         <v>0.01054892468938557</v>
       </c>
       <c r="H186" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I186">
         <v>6</v>
@@ -7573,7 +7570,7 @@
         <v>0.009815395146689493</v>
       </c>
       <c r="H187" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I187">
         <v>6</v>
@@ -7608,7 +7605,7 @@
         <v>0.00952478508615057</v>
       </c>
       <c r="H188" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I188">
         <v>6</v>
@@ -7643,7 +7640,7 @@
         <v>0.009485965072828612</v>
       </c>
       <c r="H189" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I189">
         <v>6</v>
@@ -7678,7 +7675,7 @@
         <v>0.009240415448718491</v>
       </c>
       <c r="H190" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I190">
         <v>6</v>
@@ -7713,7 +7710,7 @@
         <v>0.008879693733382259</v>
       </c>
       <c r="H191" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I191">
         <v>6</v>
@@ -7748,7 +7745,7 @@
         <v>0.008803883792551703</v>
       </c>
       <c r="H192" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I192">
         <v>6</v>
@@ -7818,7 +7815,7 @@
         <v>0.008326066390119975</v>
       </c>
       <c r="H194" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I194">
         <v>6</v>
@@ -7853,7 +7850,7 @@
         <v>0.007615751039152497</v>
       </c>
       <c r="H195" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I195">
         <v>6</v>
@@ -7923,7 +7920,7 @@
         <v>0.006457754312363775</v>
       </c>
       <c r="H197" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I197">
         <v>6</v>
@@ -7958,7 +7955,7 @@
         <v>0.006195987378103411</v>
       </c>
       <c r="H198" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I198">
         <v>6</v>
@@ -7993,7 +7990,7 @@
         <v>0.005837746478898274</v>
       </c>
       <c r="H199" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I199">
         <v>6</v>
@@ -8028,7 +8025,7 @@
         <v>0.005568686906881944</v>
       </c>
       <c r="H200" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I200">
         <v>6</v>
@@ -8063,7 +8060,7 @@
         <v>0.005474593464250786</v>
       </c>
       <c r="H201" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I201">
         <v>6</v>
@@ -8133,7 +8130,7 @@
         <v>0.0281641169698765</v>
       </c>
       <c r="H203" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I203">
         <v>6</v>
@@ -8168,7 +8165,7 @@
         <v>0.02415907455203036</v>
       </c>
       <c r="H204" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I204">
         <v>6</v>
@@ -8203,7 +8200,7 @@
         <v>0.02215983253938904</v>
       </c>
       <c r="H205" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I205">
         <v>6</v>
@@ -8238,7 +8235,7 @@
         <v>0.01518217236973045</v>
       </c>
       <c r="H206" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I206">
         <v>6</v>
@@ -8273,7 +8270,7 @@
         <v>0.01344066465705063</v>
       </c>
       <c r="H207" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I207">
         <v>6</v>
@@ -8308,7 +8305,7 @@
         <v>0.0119426658577791</v>
       </c>
       <c r="H208" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I208">
         <v>6</v>
@@ -8343,7 +8340,7 @@
         <v>0.01077490221742417</v>
       </c>
       <c r="H209" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I209">
         <v>6</v>
@@ -8378,7 +8375,7 @@
         <v>0.01039777592869933</v>
       </c>
       <c r="H210" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I210">
         <v>6</v>
@@ -8448,7 +8445,7 @@
         <v>0.009546002949577114</v>
       </c>
       <c r="H212" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I212">
         <v>6</v>
@@ -8483,7 +8480,7 @@
         <v>0.009308155985504822</v>
       </c>
       <c r="H213" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I213">
         <v>6</v>
@@ -8518,7 +8515,7 @@
         <v>0.008294282660167704</v>
       </c>
       <c r="H214" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I214">
         <v>6</v>
@@ -8553,7 +8550,7 @@
         <v>0.008268546323498011</v>
       </c>
       <c r="H215" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I215">
         <v>6</v>
@@ -8588,7 +8585,7 @@
         <v>0.008215405680823719</v>
       </c>
       <c r="H216" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I216">
         <v>6</v>
@@ -8623,7 +8620,7 @@
         <v>0.008132891348585549</v>
       </c>
       <c r="H217" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I217">
         <v>6</v>
@@ -8658,7 +8655,7 @@
         <v>0.007517284100647934</v>
       </c>
       <c r="H218" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I218">
         <v>6</v>
@@ -8693,7 +8690,7 @@
         <v>0.00737065612730746</v>
       </c>
       <c r="H219" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I219">
         <v>6</v>
@@ -8728,7 +8725,7 @@
         <v>0.007136580578237899</v>
       </c>
       <c r="H220" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I220">
         <v>6</v>
@@ -8763,7 +8760,7 @@
         <v>0.006528083368099594</v>
       </c>
       <c r="H221" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I221">
         <v>6</v>
@@ -8798,7 +8795,7 @@
         <v>0.006477496072222251</v>
       </c>
       <c r="H222" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I222">
         <v>6</v>
@@ -8833,7 +8830,7 @@
         <v>0.006417470780276859</v>
       </c>
       <c r="H223" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I223">
         <v>6</v>
@@ -8903,7 +8900,7 @@
         <v>0.00623097842904666</v>
       </c>
       <c r="H225" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I225">
         <v>6</v>
@@ -8938,7 +8935,7 @@
         <v>0.00620343218999051</v>
       </c>
       <c r="H226" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I226">
         <v>6</v>
@@ -9008,7 +9005,7 @@
         <v>0.03176925022242428</v>
       </c>
       <c r="H228" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I228">
         <v>6</v>
@@ -9043,7 +9040,7 @@
         <v>0.02417059347294252</v>
       </c>
       <c r="H229" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I229">
         <v>6</v>
@@ -9078,7 +9075,7 @@
         <v>0.01388048469001278</v>
       </c>
       <c r="H230" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I230">
         <v>6</v>
@@ -9113,7 +9110,7 @@
         <v>0.01341196161401321</v>
       </c>
       <c r="H231" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I231">
         <v>6</v>
@@ -9148,7 +9145,7 @@
         <v>0.01116620445472491</v>
       </c>
       <c r="H232" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I232">
         <v>6</v>
@@ -9183,7 +9180,7 @@
         <v>0.01077578188053076</v>
       </c>
       <c r="H233" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I233">
         <v>6</v>
@@ -9253,7 +9250,7 @@
         <v>0.009428249465321724</v>
       </c>
       <c r="H235" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I235">
         <v>6</v>
@@ -9288,7 +9285,7 @@
         <v>0.009190163536311479</v>
       </c>
       <c r="H236" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I236">
         <v>6</v>
@@ -9323,7 +9320,7 @@
         <v>0.009015345265759615</v>
       </c>
       <c r="H237" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I237">
         <v>6</v>
@@ -9358,7 +9355,7 @@
         <v>0.008999411343590889</v>
       </c>
       <c r="H238" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I238">
         <v>6</v>
@@ -9393,7 +9390,7 @@
         <v>0.008768695669482107</v>
       </c>
       <c r="H239" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I239">
         <v>6</v>
@@ -9428,7 +9425,7 @@
         <v>0.008687720385684172</v>
       </c>
       <c r="H240" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I240">
         <v>6</v>
@@ -9463,7 +9460,7 @@
         <v>0.007788336811373681</v>
       </c>
       <c r="H241" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I241">
         <v>6</v>
@@ -9498,7 +9495,7 @@
         <v>0.0077638915057603</v>
       </c>
       <c r="H242" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I242">
         <v>6</v>
@@ -9533,7 +9530,7 @@
         <v>0.007591389671677396</v>
       </c>
       <c r="H243" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I243">
         <v>6</v>
@@ -9568,7 +9565,7 @@
         <v>0.007577652086738793</v>
       </c>
       <c r="H244" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I244">
         <v>6</v>
@@ -9603,7 +9600,7 @@
         <v>0.007438434779997035</v>
       </c>
       <c r="H245" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I245">
         <v>6</v>
@@ -9638,7 +9635,7 @@
         <v>0.007243158184599173</v>
       </c>
       <c r="H246" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I246">
         <v>6</v>
@@ -9673,7 +9670,7 @@
         <v>0.006677030521890712</v>
       </c>
       <c r="H247" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I247">
         <v>6</v>
@@ -9708,7 +9705,7 @@
         <v>0.006569975708127624</v>
       </c>
       <c r="H248" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I248">
         <v>6</v>
@@ -9743,7 +9740,7 @@
         <v>0.006514523456881153</v>
       </c>
       <c r="H249" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I249">
         <v>6</v>
@@ -9778,7 +9775,7 @@
         <v>0.006397200407554478</v>
       </c>
       <c r="H250" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I250">
         <v>6</v>
@@ -9813,7 +9810,7 @@
         <v>0.006381062699153947</v>
       </c>
       <c r="H251" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I251">
         <v>6</v>
@@ -9883,7 +9880,7 @@
         <v>0.03839841642241958</v>
       </c>
       <c r="H253" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I253">
         <v>6</v>
@@ -9918,7 +9915,7 @@
         <v>0.0308103926070505</v>
       </c>
       <c r="H254" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I254">
         <v>6</v>
@@ -9953,7 +9950,7 @@
         <v>0.01315499703558166</v>
       </c>
       <c r="H255" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I255">
         <v>6</v>
@@ -9988,7 +9985,7 @@
         <v>0.01211997672479083</v>
       </c>
       <c r="H256" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I256">
         <v>6</v>
@@ -10058,7 +10055,7 @@
         <v>0.01043819415366705</v>
       </c>
       <c r="H258" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I258">
         <v>6</v>
@@ -10093,7 +10090,7 @@
         <v>0.01035195229023891</v>
       </c>
       <c r="H259" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I259">
         <v>6</v>
@@ -10128,7 +10125,7 @@
         <v>0.01009653646971111</v>
       </c>
       <c r="H260" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I260">
         <v>6</v>
@@ -10163,7 +10160,7 @@
         <v>0.009544308524170942</v>
       </c>
       <c r="H261" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I261">
         <v>6</v>
@@ -10198,7 +10195,7 @@
         <v>0.00879323522156265</v>
       </c>
       <c r="H262" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I262">
         <v>6</v>
@@ -10233,7 +10230,7 @@
         <v>0.008708044193883843</v>
       </c>
       <c r="H263" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I263">
         <v>6</v>
@@ -10268,7 +10265,7 @@
         <v>0.008480595612780521</v>
       </c>
       <c r="H264" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I264">
         <v>6</v>
@@ -10303,7 +10300,7 @@
         <v>0.008439206179010532</v>
       </c>
       <c r="H265" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I265">
         <v>6</v>
@@ -10338,7 +10335,7 @@
         <v>0.007874703865746896</v>
       </c>
       <c r="H266" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I266">
         <v>6</v>
@@ -10373,7 +10370,7 @@
         <v>0.0076937506774814</v>
       </c>
       <c r="H267" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I267">
         <v>6</v>
@@ -10408,7 +10405,7 @@
         <v>0.007460141867880972</v>
       </c>
       <c r="H268" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I268">
         <v>6</v>
@@ -10443,7 +10440,7 @@
         <v>0.007174938663124757</v>
       </c>
       <c r="H269" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I269">
         <v>6</v>
@@ -10478,7 +10475,7 @@
         <v>0.007043752292914727</v>
       </c>
       <c r="H270" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I270">
         <v>6</v>
@@ -10513,7 +10510,7 @@
         <v>0.006883709453165354</v>
       </c>
       <c r="H271" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I271">
         <v>6</v>
@@ -10548,7 +10545,7 @@
         <v>0.006723783214200894</v>
       </c>
       <c r="H272" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I272">
         <v>6</v>
@@ -10583,7 +10580,7 @@
         <v>0.006659177965246075</v>
       </c>
       <c r="H273" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I273">
         <v>6</v>
@@ -10618,7 +10615,7 @@
         <v>0.006454810377141232</v>
       </c>
       <c r="H274" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I274">
         <v>6</v>
@@ -10653,7 +10650,7 @@
         <v>0.00640248532908698</v>
       </c>
       <c r="H275" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I275">
         <v>6</v>
@@ -10688,7 +10685,7 @@
         <v>0.005848448254370739</v>
       </c>
       <c r="H276" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I276">
         <v>6</v>
@@ -10723,7 +10720,7 @@
         <v>0.04370354324556846</v>
       </c>
       <c r="H277" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I277">
         <v>6</v>
@@ -10758,7 +10755,7 @@
         <v>0.03500500008996568</v>
       </c>
       <c r="H278" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I278">
         <v>6</v>
@@ -10793,7 +10790,7 @@
         <v>0.02663542815461502</v>
       </c>
       <c r="H279" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I279">
         <v>6</v>
@@ -10828,7 +10825,7 @@
         <v>0.01519979638920298</v>
       </c>
       <c r="H280" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I280">
         <v>6</v>
@@ -10863,7 +10860,7 @@
         <v>0.01457831671934487</v>
       </c>
       <c r="H281" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I281">
         <v>6</v>
@@ -10898,7 +10895,7 @@
         <v>0.01411838113492757</v>
       </c>
       <c r="H282" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I282">
         <v>6</v>
@@ -10933,7 +10930,7 @@
         <v>0.01338257836086681</v>
       </c>
       <c r="H283" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I283">
         <v>6</v>
@@ -10968,7 +10965,7 @@
         <v>0.01249243318887912</v>
       </c>
       <c r="H284" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I284">
         <v>6</v>
@@ -11003,7 +11000,7 @@
         <v>0.01185833084517513</v>
       </c>
       <c r="H285" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I285">
         <v>6</v>
@@ -11038,7 +11035,7 @@
         <v>0.01163244791397744</v>
       </c>
       <c r="H286" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I286">
         <v>6</v>
@@ -11073,7 +11070,7 @@
         <v>0.01089611889263107</v>
       </c>
       <c r="H287" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I287">
         <v>6</v>
@@ -11108,7 +11105,7 @@
         <v>0.009961737449539272</v>
       </c>
       <c r="H288" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I288">
         <v>6</v>
@@ -11143,7 +11140,7 @@
         <v>0.008794683080557295</v>
       </c>
       <c r="H289" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I289">
         <v>6</v>
@@ -11178,7 +11175,7 @@
         <v>0.008782107295983589</v>
       </c>
       <c r="H290" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I290">
         <v>6</v>
@@ -11213,7 +11210,7 @@
         <v>0.008078315369604376</v>
       </c>
       <c r="H291" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I291">
         <v>6</v>
@@ -11248,7 +11245,7 @@
         <v>0.007622883808668799</v>
       </c>
       <c r="H292" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I292">
         <v>6</v>
@@ -11283,7 +11280,7 @@
         <v>0.007396926463271234</v>
       </c>
       <c r="H293" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I293">
         <v>6</v>
@@ -11318,7 +11315,7 @@
         <v>0.00723396994727439</v>
       </c>
       <c r="H294" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I294">
         <v>6</v>
@@ -11353,7 +11350,7 @@
         <v>0.007185765974137274</v>
       </c>
       <c r="H295" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I295">
         <v>6</v>
@@ -11388,7 +11385,7 @@
         <v>0.007163121121484329</v>
       </c>
       <c r="H296" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I296">
         <v>6</v>
@@ -11423,7 +11420,7 @@
         <v>0.006991003718382256</v>
       </c>
       <c r="H297" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I297">
         <v>6</v>
@@ -11458,7 +11455,7 @@
         <v>0.006756918922616881</v>
       </c>
       <c r="H298" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I298">
         <v>6</v>
@@ -11493,7 +11490,7 @@
         <v>0.006563754921179523</v>
       </c>
       <c r="H299" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I299">
         <v>6</v>
@@ -11528,7 +11525,7 @@
         <v>0.006450695546235834</v>
       </c>
       <c r="H300" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I300">
         <v>6</v>
@@ -11563,7 +11560,7 @@
         <v>0.006346277028231318</v>
       </c>
       <c r="H301" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I301">
         <v>6</v>
@@ -11595,10 +11592,10 @@
         <v>2254243547.77</v>
       </c>
       <c r="G302">
-        <v>0.1216678553769307</v>
+        <v>0.1216694883754951</v>
       </c>
       <c r="H302" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I302">
         <v>6</v>
@@ -11607,7 +11604,7 @@
         <v>1</v>
       </c>
       <c r="K302">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="303" spans="1:11">
@@ -11630,10 +11627,10 @@
         <v>677368701.602</v>
       </c>
       <c r="G303">
-        <v>0.0365594912337219</v>
+        <v>0.03655998192698279</v>
       </c>
       <c r="H303" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I303">
         <v>6</v>
@@ -11642,7 +11639,7 @@
         <v>1</v>
       </c>
       <c r="K303">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="304" spans="1:11">
@@ -11665,10 +11662,10 @@
         <v>664260531.11</v>
       </c>
       <c r="G304">
-        <v>0.03585200645761841</v>
+        <v>0.03585248765517791</v>
       </c>
       <c r="H304" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I304">
         <v>6</v>
@@ -11677,7 +11674,7 @@
         <v>1</v>
       </c>
       <c r="K304">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="305" spans="1:11">
@@ -11697,13 +11694,13 @@
         <v>114</v>
       </c>
       <c r="F305">
-        <v>275787976.22</v>
+        <v>275787977.309</v>
       </c>
       <c r="G305">
-        <v>0.01488505163456053</v>
+        <v>0.01488525147714975</v>
       </c>
       <c r="H305" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I305">
         <v>6</v>
@@ -11712,7 +11709,7 @@
         <v>1</v>
       </c>
       <c r="K305">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="306" spans="1:11">
@@ -11735,10 +11732,10 @@
         <v>271282812.919</v>
       </c>
       <c r="G306">
-        <v>0.01464189531833296</v>
+        <v>0.01464209183855567</v>
       </c>
       <c r="H306" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I306">
         <v>6</v>
@@ -11747,7 +11744,7 @@
         <v>1</v>
       </c>
       <c r="K306">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="307" spans="1:11">
@@ -11770,10 +11767,10 @@
         <v>226207044.223</v>
       </c>
       <c r="G307">
-        <v>0.01220902948529811</v>
+        <v>0.0122091933521433</v>
       </c>
       <c r="H307" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I307">
         <v>6</v>
@@ -11782,7 +11779,7 @@
         <v>1</v>
       </c>
       <c r="K307">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="308" spans="1:11">
@@ -11805,10 +11802,10 @@
         <v>226070073.669</v>
       </c>
       <c r="G308">
-        <v>0.01220163679981323</v>
+        <v>0.01220180056743547</v>
       </c>
       <c r="H308" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I308">
         <v>6</v>
@@ -11817,7 +11814,7 @@
         <v>1</v>
       </c>
       <c r="K308">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="309" spans="1:11">
@@ -11840,10 +11837,10 @@
         <v>182460948.844</v>
       </c>
       <c r="G309">
-        <v>0.009847929855605101</v>
+        <v>0.00984806203230261</v>
       </c>
       <c r="H309" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I309">
         <v>6</v>
@@ -11852,7 +11849,7 @@
         <v>1</v>
       </c>
       <c r="K309">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="310" spans="1:11">
@@ -11872,13 +11869,13 @@
         <v>108</v>
       </c>
       <c r="F310">
-        <v>177443665.836</v>
+        <v>177245464.913</v>
       </c>
       <c r="G310">
-        <v>0.009577133000488736</v>
+        <v>0.009566563938565966</v>
       </c>
       <c r="H310" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I310">
         <v>6</v>
@@ -11887,7 +11884,7 @@
         <v>1</v>
       </c>
       <c r="K310">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="311" spans="1:11">
@@ -11910,10 +11907,10 @@
         <v>167912997.298</v>
       </c>
       <c r="G311">
-        <v>0.009062736052353314</v>
+        <v>0.009062857690356363</v>
       </c>
       <c r="H311" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I311">
         <v>6</v>
@@ -11922,7 +11919,7 @@
         <v>1</v>
       </c>
       <c r="K311">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="312" spans="1:11">
@@ -11945,10 +11942,10 @@
         <v>137736878.327</v>
       </c>
       <c r="G312">
-        <v>0.007434046161044694</v>
+        <v>0.007434145939138679</v>
       </c>
       <c r="H312" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I312">
         <v>6</v>
@@ -11957,7 +11954,7 @@
         <v>1</v>
       </c>
       <c r="K312">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="313" spans="1:11">
@@ -11980,10 +11977,10 @@
         <v>133712469.026</v>
       </c>
       <c r="G313">
-        <v>0.007216837488407695</v>
+        <v>0.007216934351175775</v>
       </c>
       <c r="H313" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I313">
         <v>6</v>
@@ -11992,7 +11989,7 @@
         <v>1</v>
       </c>
       <c r="K313">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="314" spans="1:11">
@@ -12015,10 +12012,10 @@
         <v>122256226.849</v>
       </c>
       <c r="G314">
-        <v>0.006598511922949963</v>
+        <v>0.006598600486691504</v>
       </c>
       <c r="H314" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I314">
         <v>6</v>
@@ -12027,7 +12024,7 @@
         <v>1</v>
       </c>
       <c r="K314">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="315" spans="1:11">
@@ -12050,10 +12047,10 @@
         <v>114777667.392</v>
       </c>
       <c r="G315">
-        <v>0.006194873065319797</v>
+        <v>0.00619495621151146</v>
       </c>
       <c r="H315" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I315">
         <v>6</v>
@@ -12062,7 +12059,7 @@
         <v>1</v>
       </c>
       <c r="K315">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="316" spans="1:11">
@@ -12085,10 +12082,10 @@
         <v>107384774.414</v>
       </c>
       <c r="G316">
-        <v>0.005795857868157877</v>
+        <v>0.005795935658857393</v>
       </c>
       <c r="H316" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I316">
         <v>6</v>
@@ -12097,7 +12094,7 @@
         <v>1</v>
       </c>
       <c r="K316">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="317" spans="1:11">
@@ -12120,10 +12117,10 @@
         <v>101624075.535</v>
       </c>
       <c r="G317">
-        <v>0.005484936770580123</v>
+        <v>0.005485010388166663</v>
       </c>
       <c r="H317" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I317">
         <v>6</v>
@@ -12132,7 +12129,7 @@
         <v>1</v>
       </c>
       <c r="K317">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="318" spans="1:11">
@@ -12155,10 +12152,10 @@
         <v>101376072.213</v>
       </c>
       <c r="G318">
-        <v>0.005471551334767767</v>
+        <v>0.005471624772698</v>
       </c>
       <c r="H318" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I318">
         <v>6</v>
@@ -12167,7 +12164,7 @@
         <v>1</v>
       </c>
       <c r="K318">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="319" spans="1:11">
@@ -12190,10 +12187,10 @@
         <v>100932009.125</v>
       </c>
       <c r="G319">
-        <v>0.005447584002745251</v>
+        <v>0.00544765711899135</v>
       </c>
       <c r="H319" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I319">
         <v>6</v>
@@ -12202,7 +12199,7 @@
         <v>1</v>
       </c>
       <c r="K319">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="320" spans="1:11">
@@ -12225,10 +12222,10 @@
         <v>99948131.53</v>
       </c>
       <c r="G320">
-        <v>0.005394481365696348</v>
+        <v>0.005394553769210807</v>
       </c>
       <c r="H320" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I320">
         <v>6</v>
@@ -12237,7 +12234,7 @@
         <v>1</v>
       </c>
       <c r="K320">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="321" spans="1:11">
@@ -12260,10 +12257,10 @@
         <v>99919884.433</v>
       </c>
       <c r="G321">
-        <v>0.005392956790538524</v>
+        <v>0.005393029173590479</v>
       </c>
       <c r="H321" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I321">
         <v>6</v>
@@ -12272,7 +12269,7 @@
         <v>1</v>
       </c>
       <c r="K321">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="322" spans="1:11">
@@ -12295,10 +12292,10 @@
         <v>96187833.358</v>
       </c>
       <c r="G322">
-        <v>0.005191527512454705</v>
+        <v>0.005191597191968236</v>
       </c>
       <c r="H322" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I322">
         <v>6</v>
@@ -12307,7 +12304,7 @@
         <v>1</v>
       </c>
       <c r="K322">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="323" spans="1:11">
@@ -12330,10 +12327,10 @@
         <v>93585203.73</v>
       </c>
       <c r="G323">
-        <v>0.005051056281876062</v>
+        <v>0.005051124076016359</v>
       </c>
       <c r="H323" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I323">
         <v>6</v>
@@ -12342,7 +12339,7 @@
         <v>1</v>
       </c>
       <c r="K323">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="324" spans="1:11">
@@ -12365,10 +12362,10 @@
         <v>91316015.11300001</v>
       </c>
       <c r="G324">
-        <v>0.004928581799139158</v>
+        <v>0.00492864794945452</v>
       </c>
       <c r="H324" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I324">
         <v>6</v>
@@ -12377,7 +12374,7 @@
         <v>1</v>
       </c>
       <c r="K324">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="325" spans="1:11">
@@ -12400,10 +12397,10 @@
         <v>87282770.92</v>
       </c>
       <c r="G325">
-        <v>0.004710896282567886</v>
+        <v>0.004710959511157251</v>
       </c>
       <c r="H325" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I325">
         <v>6</v>
@@ -12412,7 +12409,7 @@
         <v>1</v>
       </c>
       <c r="K325">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="326" spans="1:11">
@@ -12435,10 +12432,10 @@
         <v>84766653.00300001</v>
       </c>
       <c r="G326">
-        <v>0.004575094332002386</v>
+        <v>0.004575155737888542</v>
       </c>
       <c r="H326" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I326">
         <v>6</v>
@@ -12447,7 +12444,7 @@
         <v>1</v>
       </c>
       <c r="K326">
-        <v>18527848138.576</v>
+        <v>18527599465.307</v>
       </c>
     </row>
     <row r="327" spans="1:11">
@@ -12473,7 +12470,7 @@
         <v>0.07455272113188458</v>
       </c>
       <c r="H327" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I327">
         <v>6</v>
@@ -12508,7 +12505,7 @@
         <v>0.05890480126564619</v>
       </c>
       <c r="H328" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I328">
         <v>6</v>
@@ -12543,7 +12540,7 @@
         <v>0.04074927259307302</v>
       </c>
       <c r="H329" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I329">
         <v>6</v>
@@ -12578,7 +12575,7 @@
         <v>0.02691955619277413</v>
       </c>
       <c r="H330" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I330">
         <v>6</v>
@@ -12613,7 +12610,7 @@
         <v>0.01660572224864261</v>
       </c>
       <c r="H331" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I331">
         <v>6</v>
@@ -12648,7 +12645,7 @@
         <v>0.01605336993245715</v>
       </c>
       <c r="H332" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I332">
         <v>6</v>
@@ -12683,7 +12680,7 @@
         <v>0.01400259141147821</v>
       </c>
       <c r="H333" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I333">
         <v>6</v>
@@ -12718,7 +12715,7 @@
         <v>0.01260248900616261</v>
       </c>
       <c r="H334" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I334">
         <v>6</v>
@@ -12753,7 +12750,7 @@
         <v>0.01227466374415092</v>
       </c>
       <c r="H335" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I335">
         <v>6</v>
@@ -12788,7 +12785,7 @@
         <v>0.01063765110877948</v>
       </c>
       <c r="H336" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I336">
         <v>6</v>
@@ -12823,7 +12820,7 @@
         <v>0.01036030089654958</v>
       </c>
       <c r="H337" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I337">
         <v>6</v>
@@ -12858,7 +12855,7 @@
         <v>0.01021452446923638</v>
       </c>
       <c r="H338" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I338">
         <v>6</v>
@@ -12893,7 +12890,7 @@
         <v>0.009887046268222614</v>
       </c>
       <c r="H339" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I339">
         <v>6</v>
@@ -12928,7 +12925,7 @@
         <v>0.009746771847334544</v>
       </c>
       <c r="H340" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I340">
         <v>6</v>
@@ -12963,7 +12960,7 @@
         <v>0.009659679170242033</v>
       </c>
       <c r="H341" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I341">
         <v>6</v>
@@ -12998,7 +12995,7 @@
         <v>0.009638699659748498</v>
       </c>
       <c r="H342" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I342">
         <v>6</v>
@@ -13033,7 +13030,7 @@
         <v>0.008460233408764731</v>
       </c>
       <c r="H343" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I343">
         <v>6</v>
@@ -13068,7 +13065,7 @@
         <v>0.007658809701161257</v>
       </c>
       <c r="H344" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I344">
         <v>6</v>
@@ -13103,7 +13100,7 @@
         <v>0.007450915956363039</v>
       </c>
       <c r="H345" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I345">
         <v>6</v>
@@ -13138,7 +13135,7 @@
         <v>0.006808749112889607</v>
       </c>
       <c r="H346" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I346">
         <v>6</v>
@@ -13173,7 +13170,7 @@
         <v>0.006694631647460028</v>
       </c>
       <c r="H347" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I347">
         <v>6</v>
@@ -13208,7 +13205,7 @@
         <v>0.006523683551797915</v>
       </c>
       <c r="H348" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I348">
         <v>6</v>
@@ -13243,7 +13240,7 @@
         <v>0.006021401148893</v>
       </c>
       <c r="H349" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I349">
         <v>6</v>
@@ -13278,7 +13275,7 @@
         <v>0.005919561371442278</v>
       </c>
       <c r="H350" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I350">
         <v>6</v>
@@ -13313,7 +13310,7 @@
         <v>0.005491242107759482</v>
       </c>
       <c r="H351" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I351">
         <v>6</v>
@@ -13345,10 +13342,10 @@
         <v>378477013.251</v>
       </c>
       <c r="G352">
-        <v>0.03186574332290047</v>
+        <v>0.03186572929148575</v>
       </c>
       <c r="H352" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I352">
         <v>6</v>
@@ -13357,7 +13354,7 @@
         <v>1</v>
       </c>
       <c r="K352">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="353" spans="1:11">
@@ -13380,10 +13377,10 @@
         <v>260444532.567</v>
       </c>
       <c r="G353">
-        <v>0.02192803878191904</v>
+        <v>0.02192802912636502</v>
       </c>
       <c r="H353" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I353">
         <v>6</v>
@@ -13392,7 +13389,7 @@
         <v>1</v>
       </c>
       <c r="K353">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="354" spans="1:11">
@@ -13415,10 +13412,10 @@
         <v>258351820.677</v>
       </c>
       <c r="G354">
-        <v>0.02175184361655691</v>
+        <v>0.02175183403858676</v>
       </c>
       <c r="H354" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I354">
         <v>6</v>
@@ -13427,7 +13424,7 @@
         <v>1</v>
       </c>
       <c r="K354">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="355" spans="1:11">
@@ -13450,10 +13447,10 @@
         <v>242314697.443</v>
       </c>
       <c r="G355">
-        <v>0.02040160348381348</v>
+        <v>0.02040159450039337</v>
       </c>
       <c r="H355" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I355">
         <v>6</v>
@@ -13462,7 +13459,7 @@
         <v>1</v>
       </c>
       <c r="K355">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="356" spans="1:11">
@@ -13485,10 +13482,10 @@
         <v>219436926.258</v>
       </c>
       <c r="G356">
-        <v>0.01847541732492571</v>
+        <v>0.01847540918966146</v>
       </c>
       <c r="H356" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I356">
         <v>6</v>
@@ -13497,7 +13494,7 @@
         <v>1</v>
       </c>
       <c r="K356">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="357" spans="1:11">
@@ -13520,10 +13517,10 @@
         <v>209923974.694</v>
       </c>
       <c r="G357">
-        <v>0.01767447760555477</v>
+        <v>0.0176744698229676</v>
       </c>
       <c r="H357" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I357">
         <v>6</v>
@@ -13532,7 +13529,7 @@
         <v>1</v>
       </c>
       <c r="K357">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="358" spans="1:11">
@@ -13555,10 +13552,10 @@
         <v>193068143.632</v>
       </c>
       <c r="G358">
-        <v>0.0162553066458652</v>
+        <v>0.01625529948818033</v>
       </c>
       <c r="H358" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I358">
         <v>6</v>
@@ -13567,7 +13564,7 @@
         <v>1</v>
       </c>
       <c r="K358">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="359" spans="1:11">
@@ -13590,10 +13587,10 @@
         <v>179634584.744</v>
       </c>
       <c r="G359">
-        <v>0.01512427272715747</v>
+        <v>0.01512426606749977</v>
       </c>
       <c r="H359" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I359">
         <v>6</v>
@@ -13602,7 +13599,7 @@
         <v>1</v>
       </c>
       <c r="K359">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="360" spans="1:11">
@@ -13625,10 +13622,10 @@
         <v>174788418.212</v>
       </c>
       <c r="G360">
-        <v>0.01471625138530036</v>
+        <v>0.01471624490530634</v>
       </c>
       <c r="H360" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I360">
         <v>6</v>
@@ -13637,7 +13634,7 @@
         <v>1</v>
       </c>
       <c r="K360">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="361" spans="1:11">
@@ -13660,10 +13657,10 @@
         <v>169535612.287</v>
       </c>
       <c r="G361">
-        <v>0.01427399317814194</v>
+        <v>0.01427398689288709</v>
       </c>
       <c r="H361" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I361">
         <v>6</v>
@@ -13672,7 +13669,7 @@
         <v>1</v>
       </c>
       <c r="K361">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="362" spans="1:11">
@@ -13695,10 +13692,10 @@
         <v>135846856.628</v>
       </c>
       <c r="G362">
-        <v>0.01143757986078767</v>
+        <v>0.0114375748244882</v>
       </c>
       <c r="H362" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I362">
         <v>6</v>
@@ -13707,7 +13704,7 @@
         <v>1</v>
       </c>
       <c r="K362">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="363" spans="1:11">
@@ -13730,10 +13727,10 @@
         <v>132867734.638</v>
       </c>
       <c r="G363">
-        <v>0.01118675369872961</v>
+        <v>0.0111867487728762</v>
       </c>
       <c r="H363" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I363">
         <v>6</v>
@@ -13742,7 +13739,7 @@
         <v>1</v>
       </c>
       <c r="K363">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="364" spans="1:11">
@@ -13765,10 +13762,10 @@
         <v>124660219.13</v>
       </c>
       <c r="G364">
-        <v>0.01049572472381217</v>
+        <v>0.01049572010223894</v>
       </c>
       <c r="H364" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I364">
         <v>6</v>
@@ -13777,7 +13774,7 @@
         <v>1</v>
       </c>
       <c r="K364">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="365" spans="1:11">
@@ -13800,10 +13797,10 @@
         <v>115545279.188</v>
       </c>
       <c r="G365">
-        <v>0.009728295457499498</v>
+        <v>0.009728291173847721</v>
       </c>
       <c r="H365" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I365">
         <v>6</v>
@@ -13812,7 +13809,7 @@
         <v>1</v>
       </c>
       <c r="K365">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="366" spans="1:11">
@@ -13835,10 +13832,10 @@
         <v>113749075.957</v>
       </c>
       <c r="G366">
-        <v>0.009577064737770551</v>
+        <v>0.009577060520710064</v>
       </c>
       <c r="H366" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I366">
         <v>6</v>
@@ -13847,7 +13844,7 @@
         <v>1</v>
       </c>
       <c r="K366">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="367" spans="1:11">
@@ -13870,10 +13867,10 @@
         <v>105445078.306</v>
       </c>
       <c r="G367">
-        <v>0.008877912481659169</v>
+        <v>0.008877908572455779</v>
       </c>
       <c r="H367" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I367">
         <v>6</v>
@@ -13882,7 +13879,7 @@
         <v>1</v>
       </c>
       <c r="K367">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="368" spans="1:11">
@@ -13905,10 +13902,10 @@
         <v>101727543.074</v>
       </c>
       <c r="G368">
-        <v>0.008564915867996429</v>
+        <v>0.008564912096614563</v>
       </c>
       <c r="H368" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I368">
         <v>6</v>
@@ -13917,7 +13914,7 @@
         <v>1</v>
       </c>
       <c r="K368">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="369" spans="1:11">
@@ -13940,10 +13937,10 @@
         <v>97906687.89</v>
       </c>
       <c r="G369">
-        <v>0.008243220266138114</v>
+        <v>0.008243216636408189</v>
       </c>
       <c r="H369" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I369">
         <v>6</v>
@@ -13952,7 +13949,7 @@
         <v>1</v>
       </c>
       <c r="K369">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="370" spans="1:11">
@@ -13972,13 +13969,13 @@
         <v>195</v>
       </c>
       <c r="F370">
-        <v>97192481.31200001</v>
+        <v>97197711.208</v>
       </c>
       <c r="G370">
-        <v>0.008183087886370623</v>
+        <v>0.008183524612238667</v>
       </c>
       <c r="H370" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I370">
         <v>6</v>
@@ -13987,7 +13984,7 @@
         <v>1</v>
       </c>
       <c r="K370">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="371" spans="1:11">
@@ -14010,10 +14007,10 @@
         <v>92058328.676</v>
       </c>
       <c r="G371">
-        <v>0.007750819652498069</v>
+        <v>0.007750816239586473</v>
       </c>
       <c r="H371" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I371">
         <v>6</v>
@@ -14022,7 +14019,7 @@
         <v>1</v>
       </c>
       <c r="K371">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="372" spans="1:11">
@@ -14045,10 +14042,10 @@
         <v>88670921.052</v>
       </c>
       <c r="G372">
-        <v>0.007465618020437962</v>
+        <v>0.007465614733108949</v>
       </c>
       <c r="H372" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I372">
         <v>6</v>
@@ -14057,7 +14054,7 @@
         <v>1</v>
       </c>
       <c r="K372">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="373" spans="1:11">
@@ -14080,10 +14077,10 @@
         <v>87709497.832</v>
       </c>
       <c r="G373">
-        <v>0.007384671319632968</v>
+        <v>0.007384668067947145</v>
       </c>
       <c r="H373" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I373">
         <v>6</v>
@@ -14092,7 +14089,7 @@
         <v>1</v>
       </c>
       <c r="K373">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="374" spans="1:11">
@@ -14115,10 +14112,10 @@
         <v>80663130.28399999</v>
       </c>
       <c r="G374">
-        <v>0.006791404802032139</v>
+        <v>0.00679140181157884</v>
       </c>
       <c r="H374" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I374">
         <v>6</v>
@@ -14127,7 +14124,7 @@
         <v>1</v>
       </c>
       <c r="K374">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="375" spans="1:11">
@@ -14150,10 +14147,10 @@
         <v>74026762.992</v>
       </c>
       <c r="G375">
-        <v>0.006232658116449101</v>
+        <v>0.006232655372028237</v>
       </c>
       <c r="H375" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I375">
         <v>6</v>
@@ -14162,7 +14159,7 @@
         <v>1</v>
       </c>
       <c r="K375">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="376" spans="1:11">
@@ -14185,10 +14182,10 @@
         <v>73502806.98500001</v>
       </c>
       <c r="G376">
-        <v>0.006188543818758634</v>
+        <v>0.006188541093762581</v>
       </c>
       <c r="H376" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I376">
         <v>6</v>
@@ -14197,7 +14194,7 @@
         <v>1</v>
       </c>
       <c r="K376">
-        <v>11877237866.879</v>
+        <v>11877243096.775</v>
       </c>
     </row>
     <row r="377" spans="1:11">
@@ -14220,10 +14217,10 @@
         <v>222449841.148</v>
       </c>
       <c r="G377">
-        <v>0.02149197169749797</v>
+        <v>0.02149185642105062</v>
       </c>
       <c r="H377" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I377">
         <v>6</v>
@@ -14232,7 +14229,7 @@
         <v>1</v>
       </c>
       <c r="K377">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="378" spans="1:11">
@@ -14255,10 +14252,10 @@
         <v>213822032.291</v>
       </c>
       <c r="G378">
-        <v>0.02065839670904609</v>
+        <v>0.02065828590364331</v>
       </c>
       <c r="H378" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I378">
         <v>6</v>
@@ -14267,7 +14264,7 @@
         <v>1</v>
       </c>
       <c r="K378">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="379" spans="1:11">
@@ -14290,10 +14287,10 @@
         <v>208659453.35</v>
       </c>
       <c r="G379">
-        <v>0.02015961460197211</v>
+        <v>0.02015950647188596</v>
       </c>
       <c r="H379" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I379">
         <v>6</v>
@@ -14302,7 +14299,7 @@
         <v>1</v>
       </c>
       <c r="K379">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="380" spans="1:11">
@@ -14325,10 +14322,10 @@
         <v>195302803.977</v>
       </c>
       <c r="G380">
-        <v>0.01886916310595629</v>
+        <v>0.01886906189746235</v>
       </c>
       <c r="H380" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I380">
         <v>6</v>
@@ -14337,7 +14334,7 @@
         <v>1</v>
       </c>
       <c r="K380">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="381" spans="1:11">
@@ -14360,10 +14357,10 @@
         <v>187215621.809</v>
       </c>
       <c r="G381">
-        <v>0.01808782071717243</v>
+        <v>0.01808772369956317</v>
       </c>
       <c r="H381" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I381">
         <v>6</v>
@@ -14372,7 +14369,7 @@
         <v>1</v>
       </c>
       <c r="K381">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="382" spans="1:11">
@@ -14395,10 +14392,10 @@
         <v>178038009.058</v>
       </c>
       <c r="G382">
-        <v>0.01720112647420439</v>
+        <v>0.01720103421255533</v>
       </c>
       <c r="H382" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I382">
         <v>6</v>
@@ -14407,7 +14404,7 @@
         <v>1</v>
       </c>
       <c r="K382">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="383" spans="1:11">
@@ -14430,10 +14427,10 @@
         <v>153473752.745</v>
       </c>
       <c r="G383">
-        <v>0.0148278530264709</v>
+        <v>0.01482777349434407</v>
       </c>
       <c r="H383" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I383">
         <v>6</v>
@@ -14442,7 +14439,7 @@
         <v>1</v>
       </c>
       <c r="K383">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="384" spans="1:11">
@@ -14465,10 +14462,10 @@
         <v>143405784.008</v>
       </c>
       <c r="G384">
-        <v>0.01385513711878483</v>
+        <v>0.01385506280401245</v>
       </c>
       <c r="H384" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I384">
         <v>6</v>
@@ -14477,7 +14474,7 @@
         <v>1</v>
       </c>
       <c r="K384">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="385" spans="1:11">
@@ -14500,10 +14497,10 @@
         <v>127862610.715</v>
       </c>
       <c r="G385">
-        <v>0.01235343480792451</v>
+        <v>0.01235336854782994</v>
       </c>
       <c r="H385" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I385">
         <v>6</v>
@@ -14512,7 +14509,7 @@
         <v>1</v>
       </c>
       <c r="K385">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="386" spans="1:11">
@@ -14535,10 +14532,10 @@
         <v>122720767.813</v>
       </c>
       <c r="G386">
-        <v>0.01185665611142168</v>
+        <v>0.01185659251589805</v>
       </c>
       <c r="H386" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I386">
         <v>6</v>
@@ -14547,7 +14544,7 @@
         <v>1</v>
       </c>
       <c r="K386">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="387" spans="1:11">
@@ -14570,10 +14567,10 @@
         <v>116157849.763</v>
       </c>
       <c r="G387">
-        <v>0.01122258036537628</v>
+        <v>0.01122252017084351</v>
       </c>
       <c r="H387" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I387">
         <v>6</v>
@@ -14582,7 +14579,7 @@
         <v>1</v>
       </c>
       <c r="K387">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="388" spans="1:11">
@@ -14602,13 +14599,13 @@
         <v>199</v>
       </c>
       <c r="F388">
-        <v>114274451.938</v>
+        <v>114313785.316</v>
       </c>
       <c r="G388">
-        <v>0.01104061605134875</v>
+        <v>0.01104435700326579</v>
       </c>
       <c r="H388" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I388">
         <v>6</v>
@@ -14617,7 +14614,7 @@
         <v>1</v>
       </c>
       <c r="K388">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="389" spans="1:11">
@@ -14640,10 +14637,10 @@
         <v>109080531.152</v>
       </c>
       <c r="G389">
-        <v>0.01053880585469641</v>
+        <v>0.01053874932772368</v>
       </c>
       <c r="H389" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I389">
         <v>6</v>
@@ -14652,7 +14649,7 @@
         <v>1</v>
       </c>
       <c r="K389">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="390" spans="1:11">
@@ -14675,10 +14672,10 @@
         <v>102964190.32</v>
       </c>
       <c r="G390">
-        <v>0.009947876127009453</v>
+        <v>0.009947822769605362</v>
       </c>
       <c r="H390" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I390">
         <v>6</v>
@@ -14687,7 +14684,7 @@
         <v>1</v>
       </c>
       <c r="K390">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="391" spans="1:11">
@@ -14710,10 +14707,10 @@
         <v>88914157.023</v>
       </c>
       <c r="G391">
-        <v>0.00859043340459759</v>
+        <v>0.008590387328106422</v>
       </c>
       <c r="H391" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I391">
         <v>6</v>
@@ -14722,7 +14719,7 @@
         <v>1</v>
       </c>
       <c r="K391">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="392" spans="1:11">
@@ -14745,10 +14742,10 @@
         <v>84369307.689</v>
       </c>
       <c r="G392">
-        <v>0.00815133318878429</v>
+        <v>0.00815128946749411</v>
       </c>
       <c r="H392" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I392">
         <v>6</v>
@@ -14757,7 +14754,7 @@
         <v>1</v>
       </c>
       <c r="K392">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="393" spans="1:11">
@@ -14780,10 +14777,10 @@
         <v>81992499.50300001</v>
       </c>
       <c r="G393">
-        <v>0.007921698076435942</v>
+        <v>0.007921655586839172</v>
       </c>
       <c r="H393" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I393">
         <v>6</v>
@@ -14792,7 +14789,7 @@
         <v>1</v>
       </c>
       <c r="K393">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="394" spans="1:11">
@@ -14815,10 +14812,10 @@
         <v>80585156.119</v>
       </c>
       <c r="G394">
-        <v>0.007785727720055848</v>
+        <v>0.007785685959763017</v>
       </c>
       <c r="H394" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I394">
         <v>6</v>
@@ -14827,7 +14824,7 @@
         <v>1</v>
       </c>
       <c r="K394">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="395" spans="1:11">
@@ -14850,10 +14847,10 @@
         <v>77472040.242</v>
       </c>
       <c r="G395">
-        <v>0.007484954305365022</v>
+        <v>0.007484914158329979</v>
       </c>
       <c r="H395" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I395">
         <v>6</v>
@@ -14862,7 +14859,7 @@
         <v>1</v>
       </c>
       <c r="K395">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="396" spans="1:11">
@@ -14882,13 +14879,13 @@
         <v>194</v>
       </c>
       <c r="F396">
-        <v>77341992.171</v>
+        <v>77344835.09199999</v>
       </c>
       <c r="G396">
-        <v>0.007472389722505255</v>
+        <v>0.007472624309950184</v>
       </c>
       <c r="H396" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I396">
         <v>6</v>
@@ -14897,7 +14894,7 @@
         <v>1</v>
       </c>
       <c r="K396">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="397" spans="1:11">
@@ -14920,10 +14917,10 @@
         <v>76287955.618</v>
       </c>
       <c r="G397">
-        <v>0.007370554074305656</v>
+        <v>0.007370514540878913</v>
       </c>
       <c r="H397" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I397">
         <v>6</v>
@@ -14932,7 +14929,7 @@
         <v>1</v>
       </c>
       <c r="K397">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="398" spans="1:11">
@@ -14955,10 +14952,10 @@
         <v>67438092.76799999</v>
       </c>
       <c r="G398">
-        <v>0.006515525358990032</v>
+        <v>0.006515490411679169</v>
       </c>
       <c r="H398" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I398">
         <v>6</v>
@@ -14967,7 +14964,7 @@
         <v>1</v>
       </c>
       <c r="K398">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="399" spans="1:11">
@@ -14990,10 +14987,10 @@
         <v>63894592.36499999</v>
       </c>
       <c r="G399">
-        <v>0.006173170381443971</v>
+        <v>0.006173137270421842</v>
       </c>
       <c r="H399" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I399">
         <v>6</v>
@@ -15002,7 +14999,7 @@
         <v>1</v>
       </c>
       <c r="K399">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="400" spans="1:11">
@@ -15025,10 +15022,10 @@
         <v>62442373.547</v>
       </c>
       <c r="G400">
-        <v>0.006032864388983115</v>
+        <v>0.006032832030519969</v>
       </c>
       <c r="H400" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I400">
         <v>6</v>
@@ -15037,7 +15034,7 @@
         <v>1</v>
       </c>
       <c r="K400">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="401" spans="1:11">
@@ -15060,10 +15057,10 @@
         <v>61337622.316</v>
       </c>
       <c r="G401">
-        <v>0.005926128946660946</v>
+        <v>0.005926097160694487</v>
       </c>
       <c r="H401" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I401">
         <v>6</v>
@@ -15072,7 +15069,7 @@
         <v>1</v>
       </c>
       <c r="K401">
-        <v>10350369164.775</v>
+        <v>10350424681.328</v>
       </c>
     </row>
     <row r="402" spans="1:11">
@@ -15098,7 +15095,7 @@
         <v>0.0596961436519759</v>
       </c>
       <c r="H402" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I402">
         <v>6</v>
@@ -15133,7 +15130,7 @@
         <v>0.02021260435035584</v>
       </c>
       <c r="H403" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I403">
         <v>6</v>
@@ -15168,7 +15165,7 @@
         <v>0.0197550108820954</v>
       </c>
       <c r="H404" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I404">
         <v>6</v>
@@ -15203,7 +15200,7 @@
         <v>0.01974533799112489</v>
       </c>
       <c r="H405" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I405">
         <v>6</v>
@@ -15238,7 +15235,7 @@
         <v>0.0170173372140564</v>
       </c>
       <c r="H406" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I406">
         <v>6</v>
@@ -15273,7 +15270,7 @@
         <v>0.01370887163496546</v>
       </c>
       <c r="H407" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I407">
         <v>6</v>
@@ -15308,7 +15305,7 @@
         <v>0.01357145304967261</v>
       </c>
       <c r="H408" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I408">
         <v>6</v>
@@ -15343,7 +15340,7 @@
         <v>0.0124480021140341</v>
       </c>
       <c r="H409" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I409">
         <v>6</v>
@@ -15378,7 +15375,7 @@
         <v>0.01061018133572934</v>
       </c>
       <c r="H410" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I410">
         <v>6</v>
@@ -15413,7 +15410,7 @@
         <v>0.009988801238181176</v>
       </c>
       <c r="H411" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I411">
         <v>6</v>
@@ -15448,7 +15445,7 @@
         <v>0.009518753473096015</v>
       </c>
       <c r="H412" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I412">
         <v>6</v>
@@ -15483,7 +15480,7 @@
         <v>0.008975162236176174</v>
       </c>
       <c r="H413" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I413">
         <v>6</v>
@@ -15518,7 +15515,7 @@
         <v>0.008937042301895499</v>
       </c>
       <c r="H414" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I414">
         <v>6</v>
@@ -15553,7 +15550,7 @@
         <v>0.008596296585026609</v>
       </c>
       <c r="H415" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I415">
         <v>6</v>
@@ -15588,7 +15585,7 @@
         <v>0.008163016321078775</v>
       </c>
       <c r="H416" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I416">
         <v>6</v>
@@ -15623,7 +15620,7 @@
         <v>0.007306325481518271</v>
       </c>
       <c r="H417" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I417">
         <v>6</v>
@@ -15658,7 +15655,7 @@
         <v>0.007209914072219476</v>
       </c>
       <c r="H418" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I418">
         <v>6</v>
@@ -15693,7 +15690,7 @@
         <v>0.006768269651935538</v>
       </c>
       <c r="H419" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I419">
         <v>6</v>
@@ -15728,7 +15725,7 @@
         <v>0.006637800586257444</v>
       </c>
       <c r="H420" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I420">
         <v>6</v>
@@ -15763,7 +15760,7 @@
         <v>0.006605965655344976</v>
       </c>
       <c r="H421" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I421">
         <v>6</v>
@@ -15798,7 +15795,7 @@
         <v>0.006486213312782085</v>
       </c>
       <c r="H422" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I422">
         <v>6</v>
@@ -15833,7 +15830,7 @@
         <v>0.006090003026589956</v>
       </c>
       <c r="H423" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I423">
         <v>6</v>
@@ -15868,7 +15865,7 @@
         <v>0.005997894517721434</v>
       </c>
       <c r="H424" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I424">
         <v>6</v>
@@ -15903,7 +15900,7 @@
         <v>0.005992021860080149</v>
       </c>
       <c r="H425" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I425">
         <v>6</v>
@@ -15938,7 +15935,7 @@
         <v>0.005774989217329173</v>
       </c>
       <c r="H426" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I426">
         <v>6</v>
@@ -15970,10 +15967,10 @@
         <v>216131776.714</v>
       </c>
       <c r="G427">
-        <v>0.02841478871655337</v>
+        <v>0.02846882135038202</v>
       </c>
       <c r="H427" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I427">
         <v>6</v>
@@ -15982,7 +15979,7 @@
         <v>1</v>
       </c>
       <c r="K427">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="428" spans="1:11">
@@ -16005,10 +16002,10 @@
         <v>180223772.262</v>
       </c>
       <c r="G428">
-        <v>0.02369397266974508</v>
+        <v>0.02373902835402207</v>
       </c>
       <c r="H428" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I428">
         <v>6</v>
@@ -16017,7 +16014,7 @@
         <v>1</v>
       </c>
       <c r="K428">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="429" spans="1:11">
@@ -16040,10 +16037,10 @@
         <v>155411758.186</v>
       </c>
       <c r="G429">
-        <v>0.02043194360432622</v>
+        <v>0.02047079632071249</v>
       </c>
       <c r="H429" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I429">
         <v>6</v>
@@ -16052,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="K429">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="430" spans="1:11">
@@ -16072,13 +16069,13 @@
         <v>170</v>
       </c>
       <c r="F430">
-        <v>150310966.648</v>
+        <v>150308967.21</v>
       </c>
       <c r="G430">
-        <v>0.01976134386169214</v>
+        <v>0.01979865802206556</v>
       </c>
       <c r="H430" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I430">
         <v>6</v>
@@ -16087,7 +16084,7 @@
         <v>1</v>
       </c>
       <c r="K430">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="431" spans="1:11">
@@ -16101,19 +16098,19 @@
         <v>5</v>
       </c>
       <c r="D431" t="s">
-        <v>93</v>
+        <v>27</v>
       </c>
       <c r="E431" t="s">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="F431">
-        <v>141176369.692</v>
+        <v>137711202.362</v>
       </c>
       <c r="G431">
-        <v>0.01856042076532082</v>
+        <v>0.01813928371660924</v>
       </c>
       <c r="H431" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I431">
         <v>6</v>
@@ -16122,7 +16119,7 @@
         <v>1</v>
       </c>
       <c r="K431">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="432" spans="1:11">
@@ -16136,19 +16133,19 @@
         <v>6</v>
       </c>
       <c r="D432" t="s">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="E432" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="F432">
-        <v>138047381.816</v>
+        <v>136142801.738</v>
       </c>
       <c r="G432">
-        <v>0.01814905353952483</v>
+        <v>0.01793269439481059</v>
       </c>
       <c r="H432" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I432">
         <v>6</v>
@@ -16157,7 +16154,7 @@
         <v>1</v>
       </c>
       <c r="K432">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="433" spans="1:11">
@@ -16180,10 +16177,10 @@
         <v>124476539.812</v>
       </c>
       <c r="G433">
-        <v>0.01636489845547323</v>
+        <v>0.01639601741168678</v>
       </c>
       <c r="H433" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I433">
         <v>6</v>
@@ -16192,7 +16189,7 @@
         <v>1</v>
       </c>
       <c r="K433">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="434" spans="1:11">
@@ -16212,13 +16209,13 @@
         <v>151</v>
       </c>
       <c r="F434">
-        <v>120279858.812</v>
+        <v>119976406.536</v>
       </c>
       <c r="G434">
-        <v>0.01581316189114761</v>
+        <v>0.01580326102835828</v>
       </c>
       <c r="H434" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I434">
         <v>6</v>
@@ -16227,7 +16224,7 @@
         <v>1</v>
       </c>
       <c r="K434">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="435" spans="1:11">
@@ -16247,13 +16244,13 @@
         <v>164</v>
       </c>
       <c r="F435">
-        <v>93507260.271</v>
+        <v>93463962.54499999</v>
       </c>
       <c r="G435">
-        <v>0.01229337529381501</v>
+        <v>0.01231104880941853</v>
       </c>
       <c r="H435" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I435">
         <v>6</v>
@@ -16262,7 +16259,7 @@
         <v>1</v>
       </c>
       <c r="K435">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="436" spans="1:11">
@@ -16285,10 +16282,10 @@
         <v>74547108.09100001</v>
       </c>
       <c r="G436">
-        <v>0.009800688996504332</v>
+        <v>0.009819325666482743</v>
       </c>
       <c r="H436" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I436">
         <v>6</v>
@@ -16297,7 +16294,7 @@
         <v>1</v>
       </c>
       <c r="K436">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="437" spans="1:11">
@@ -16317,13 +16314,13 @@
         <v>195</v>
       </c>
       <c r="F437">
-        <v>72091033.22</v>
+        <v>72088799.965</v>
       </c>
       <c r="G437">
-        <v>0.009477789469222649</v>
+        <v>0.009495517960242972</v>
       </c>
       <c r="H437" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I437">
         <v>6</v>
@@ -16332,7 +16329,7 @@
         <v>1</v>
       </c>
       <c r="K437">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="438" spans="1:11">
@@ -16352,13 +16349,13 @@
         <v>103</v>
       </c>
       <c r="F438">
-        <v>71173877.638</v>
+        <v>71173127.435</v>
       </c>
       <c r="G438">
-        <v>0.00935721126235757</v>
+        <v>0.009374905813022633</v>
       </c>
       <c r="H438" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I438">
         <v>6</v>
@@ -16367,7 +16364,7 @@
         <v>1</v>
       </c>
       <c r="K438">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="439" spans="1:11">
@@ -16387,13 +16384,13 @@
         <v>108</v>
       </c>
       <c r="F439">
-        <v>69725261.255</v>
+        <v>69201673.65700001</v>
       </c>
       <c r="G439">
-        <v>0.009166762041608548</v>
+        <v>0.009115226434729798</v>
       </c>
       <c r="H439" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I439">
         <v>6</v>
@@ -16402,7 +16399,7 @@
         <v>1</v>
       </c>
       <c r="K439">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="440" spans="1:11">
@@ -16425,10 +16422,10 @@
         <v>68702551</v>
       </c>
       <c r="G440">
-        <v>0.009032306589217892</v>
+        <v>0.00904948212831592</v>
       </c>
       <c r="H440" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I440">
         <v>6</v>
@@ -16437,7 +16434,7 @@
         <v>1</v>
       </c>
       <c r="K440">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="441" spans="1:11">
@@ -16457,13 +16454,13 @@
         <v>194</v>
       </c>
       <c r="F441">
-        <v>68211146.71699999</v>
+        <v>68207830.311</v>
       </c>
       <c r="G441">
-        <v>0.00896770179538264</v>
+        <v>0.008984317647980777</v>
       </c>
       <c r="H441" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I441">
         <v>6</v>
@@ -16472,7 +16469,7 @@
         <v>1</v>
       </c>
       <c r="K441">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="442" spans="1:11">
@@ -16486,19 +16483,19 @@
         <v>16</v>
       </c>
       <c r="D442" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E442" t="s">
-        <v>114</v>
+        <v>174</v>
       </c>
       <c r="F442">
-        <v>67104654.041</v>
+        <v>67092984.421</v>
       </c>
       <c r="G442">
-        <v>0.008822231489798849</v>
+        <v>0.008837470437643834</v>
       </c>
       <c r="H442" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I442">
         <v>6</v>
@@ -16507,7 +16504,7 @@
         <v>1</v>
       </c>
       <c r="K442">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="443" spans="1:11">
@@ -16521,19 +16518,19 @@
         <v>17</v>
       </c>
       <c r="D443" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E443" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="F443">
-        <v>67092984.421</v>
+        <v>66909257.488</v>
       </c>
       <c r="G443">
-        <v>0.008820697287879334</v>
+        <v>0.008813269973869588</v>
       </c>
       <c r="H443" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I443">
         <v>6</v>
@@ -16542,7 +16539,7 @@
         <v>1</v>
       </c>
       <c r="K443">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="444" spans="1:11">
@@ -16562,13 +16559,13 @@
         <v>118</v>
       </c>
       <c r="F444">
-        <v>57691208.082</v>
+        <v>57634548.12899999</v>
       </c>
       <c r="G444">
-        <v>0.007584648187211987</v>
+        <v>0.007591607672136499</v>
       </c>
       <c r="H444" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I444">
         <v>6</v>
@@ -16577,7 +16574,7 @@
         <v>1</v>
       </c>
       <c r="K444">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="445" spans="1:11">
@@ -16600,10 +16597,10 @@
         <v>51083213.994</v>
       </c>
       <c r="G445">
-        <v>0.006715896915624483</v>
+        <v>0.006728667645771125</v>
       </c>
       <c r="H445" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I445">
         <v>6</v>
@@ -16612,7 +16609,7 @@
         <v>1</v>
       </c>
       <c r="K445">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="446" spans="1:11">
@@ -16635,10 +16632,10 @@
         <v>49382582.85</v>
       </c>
       <c r="G446">
-        <v>0.006492315379506846</v>
+        <v>0.006504660954309472</v>
       </c>
       <c r="H446" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I446">
         <v>6</v>
@@ -16647,7 +16644,7 @@
         <v>1</v>
       </c>
       <c r="K446">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="447" spans="1:11">
@@ -16670,10 +16667,10 @@
         <v>46795346</v>
       </c>
       <c r="G447">
-        <v>0.006152172020810859</v>
+        <v>0.006163870790116073</v>
       </c>
       <c r="H447" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I447">
         <v>6</v>
@@ -16682,7 +16679,7 @@
         <v>1</v>
       </c>
       <c r="K447">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="448" spans="1:11">
@@ -16702,13 +16699,13 @@
         <v>169</v>
       </c>
       <c r="F448">
-        <v>44008736.202</v>
+        <v>43969672.502</v>
       </c>
       <c r="G448">
-        <v>0.005785817152269594</v>
+        <v>0.005791673812734449</v>
       </c>
       <c r="H448" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I448">
         <v>6</v>
@@ -16717,7 +16714,7 @@
         <v>1</v>
       </c>
       <c r="K448">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="449" spans="1:11">
@@ -16737,13 +16734,13 @@
         <v>203</v>
       </c>
       <c r="F449">
-        <v>43751452.543</v>
+        <v>43727503.332</v>
       </c>
       <c r="G449">
-        <v>0.005751992136245316</v>
+        <v>0.005759775352720291</v>
       </c>
       <c r="H449" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I449">
         <v>6</v>
@@ -16752,7 +16749,7 @@
         <v>1</v>
       </c>
       <c r="K449">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="450" spans="1:11">
@@ -16772,13 +16769,13 @@
         <v>165</v>
       </c>
       <c r="F450">
-        <v>43135213.946</v>
+        <v>43135208.89</v>
       </c>
       <c r="G450">
-        <v>0.005670975407474743</v>
+        <v>0.005681758483047143</v>
       </c>
       <c r="H450" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I450">
         <v>6</v>
@@ -16787,7 +16784,7 @@
         <v>1</v>
       </c>
       <c r="K450">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="451" spans="1:11">
@@ -16810,10 +16807,10 @@
         <v>41829236.814</v>
       </c>
       <c r="G451">
-        <v>0.005499278932117786</v>
+        <v>0.00550973618125748</v>
       </c>
       <c r="H451" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I451">
         <v>6</v>
@@ -16822,7 +16819,7 @@
         <v>1</v>
       </c>
       <c r="K451">
-        <v>7606312996.728</v>
+        <v>7591876532.363</v>
       </c>
     </row>
     <row r="452" spans="1:11">
@@ -16842,13 +16839,13 @@
         <v>170</v>
       </c>
       <c r="F452">
-        <v>361563537.238</v>
+        <v>361563552.675</v>
       </c>
       <c r="G452">
-        <v>0.03830909861894603</v>
+        <v>0.03825822983040678</v>
       </c>
       <c r="H452" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I452">
         <v>6</v>
@@ -16857,7 +16854,7 @@
         <v>1</v>
       </c>
       <c r="K452">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="453" spans="1:11">
@@ -16880,10 +16877,10 @@
         <v>224067487.562</v>
       </c>
       <c r="G453">
-        <v>0.02374084384693305</v>
+        <v>0.02370931852297163</v>
       </c>
       <c r="H453" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I453">
         <v>6</v>
@@ -16892,7 +16889,7 @@
         <v>1</v>
       </c>
       <c r="K453">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="454" spans="1:11">
@@ -16915,10 +16912,10 @@
         <v>219356129.053</v>
       </c>
       <c r="G454">
-        <v>0.02324165662487729</v>
+        <v>0.02321079416863002</v>
       </c>
       <c r="H454" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I454">
         <v>6</v>
@@ -16927,7 +16924,7 @@
         <v>1</v>
       </c>
       <c r="K454">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="455" spans="1:11">
@@ -16947,13 +16944,13 @@
         <v>167</v>
       </c>
       <c r="F455">
-        <v>204114743.021</v>
+        <v>204124208.698</v>
       </c>
       <c r="G455">
-        <v>0.02162677099495557</v>
+        <v>0.02159905453008339</v>
       </c>
       <c r="H455" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I455">
         <v>6</v>
@@ -16962,7 +16959,7 @@
         <v>1</v>
       </c>
       <c r="K455">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="456" spans="1:11">
@@ -16982,13 +16979,13 @@
         <v>121</v>
       </c>
       <c r="F456">
-        <v>188109917.25</v>
+        <v>188109936.836</v>
       </c>
       <c r="G456">
-        <v>0.01993099588023017</v>
+        <v>0.01990453170296167</v>
       </c>
       <c r="H456" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I456">
         <v>6</v>
@@ -16997,7 +16994,7 @@
         <v>1</v>
       </c>
       <c r="K456">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="457" spans="1:11">
@@ -17017,13 +17014,13 @@
         <v>200</v>
       </c>
       <c r="F457">
-        <v>169178489.702</v>
+        <v>172418164.588</v>
       </c>
       <c r="G457">
-        <v>0.0179251356364845</v>
+        <v>0.01824413362171477</v>
       </c>
       <c r="H457" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I457">
         <v>6</v>
@@ -17032,7 +17029,7 @@
         <v>1</v>
       </c>
       <c r="K457">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="458" spans="1:11">
@@ -17052,13 +17049,13 @@
         <v>166</v>
       </c>
       <c r="F458">
-        <v>152480249.696</v>
+        <v>152641781.235</v>
       </c>
       <c r="G458">
-        <v>0.01615589051835301</v>
+        <v>0.01615152939229068</v>
       </c>
       <c r="H458" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I458">
         <v>6</v>
@@ -17067,7 +17064,7 @@
         <v>1</v>
       </c>
       <c r="K458">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="459" spans="1:11">
@@ -17087,13 +17084,13 @@
         <v>114</v>
       </c>
       <c r="F459">
-        <v>135731442.863</v>
+        <v>135772985.25</v>
       </c>
       <c r="G459">
-        <v>0.01438128764324971</v>
+        <v>0.01436658655449176</v>
       </c>
       <c r="H459" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I459">
         <v>6</v>
@@ -17102,7 +17099,7 @@
         <v>1</v>
       </c>
       <c r="K459">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="460" spans="1:11">
@@ -17122,13 +17119,13 @@
         <v>194</v>
       </c>
       <c r="F460">
-        <v>133417183.965</v>
+        <v>133418538.336</v>
       </c>
       <c r="G460">
-        <v>0.01413608268416973</v>
+        <v>0.01411745477532631</v>
       </c>
       <c r="H460" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I460">
         <v>6</v>
@@ -17137,7 +17134,7 @@
         <v>1</v>
       </c>
       <c r="K460">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="461" spans="1:11">
@@ -17160,10 +17157,10 @@
         <v>109904998.397</v>
       </c>
       <c r="G461">
-        <v>0.01164487286098847</v>
+        <v>0.01162940970425322</v>
       </c>
       <c r="H461" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I461">
         <v>6</v>
@@ -17172,7 +17169,7 @@
         <v>1</v>
       </c>
       <c r="K461">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="462" spans="1:11">
@@ -17192,13 +17189,13 @@
         <v>151</v>
       </c>
       <c r="F462">
-        <v>107050048.555</v>
+        <v>107216306.086</v>
       </c>
       <c r="G462">
-        <v>0.01134237954021611</v>
+        <v>0.01134491031924483</v>
       </c>
       <c r="H462" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I462">
         <v>6</v>
@@ -17207,7 +17204,7 @@
         <v>1</v>
       </c>
       <c r="K462">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="463" spans="1:11">
@@ -17227,13 +17224,13 @@
         <v>164</v>
       </c>
       <c r="F463">
-        <v>97217995.598</v>
+        <v>97228861.38699999</v>
       </c>
       <c r="G463">
-        <v>0.01030063432101145</v>
+        <v>0.0102881059154661</v>
       </c>
       <c r="H463" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I463">
         <v>6</v>
@@ -17242,7 +17239,7 @@
         <v>1</v>
       </c>
       <c r="K463">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="464" spans="1:11">
@@ -17262,13 +17259,13 @@
         <v>199</v>
       </c>
       <c r="F464">
-        <v>96873091.413</v>
+        <v>96894131.027</v>
       </c>
       <c r="G464">
-        <v>0.01026409034719654</v>
+        <v>0.01025268699409157</v>
       </c>
       <c r="H464" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I464">
         <v>6</v>
@@ -17277,7 +17274,7 @@
         <v>1</v>
       </c>
       <c r="K464">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="465" spans="1:11">
@@ -17297,13 +17294,13 @@
         <v>103</v>
       </c>
       <c r="F465">
-        <v>70505673.101</v>
+        <v>70596597.874</v>
       </c>
       <c r="G465">
-        <v>0.007470357228647849</v>
+        <v>0.007470058435718677</v>
       </c>
       <c r="H465" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I465">
         <v>6</v>
@@ -17312,7 +17309,7 @@
         <v>1</v>
       </c>
       <c r="K465">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="466" spans="1:11">
@@ -17332,13 +17329,13 @@
         <v>169</v>
       </c>
       <c r="F466">
-        <v>64180755.77</v>
+        <v>64253734.049</v>
       </c>
       <c r="G466">
-        <v>0.006800207014826747</v>
+        <v>0.006798899132729005</v>
       </c>
       <c r="H466" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I466">
         <v>6</v>
@@ -17347,7 +17344,7 @@
         <v>1</v>
       </c>
       <c r="K466">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="467" spans="1:11">
@@ -17367,13 +17364,13 @@
         <v>189</v>
       </c>
       <c r="F467">
-        <v>64147459.927</v>
+        <v>64155360.75</v>
       </c>
       <c r="G467">
-        <v>0.006796679187483228</v>
+        <v>0.006788489930102045</v>
       </c>
       <c r="H467" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I467">
         <v>6</v>
@@ -17382,7 +17379,7 @@
         <v>1</v>
       </c>
       <c r="K467">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="468" spans="1:11">
@@ -17405,10 +17402,10 @@
         <v>63582499.996</v>
       </c>
       <c r="G468">
-        <v>0.006736819429837961</v>
+        <v>0.006727873647777115</v>
       </c>
       <c r="H468" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I468">
         <v>6</v>
@@ -17417,7 +17414,7 @@
         <v>1</v>
       </c>
       <c r="K468">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="469" spans="1:11">
@@ -17437,13 +17434,13 @@
         <v>108</v>
       </c>
       <c r="F469">
-        <v>63160123.899</v>
+        <v>63193908.585</v>
       </c>
       <c r="G469">
-        <v>0.006692066998002979</v>
+        <v>0.006686755511277546</v>
       </c>
       <c r="H469" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I469">
         <v>6</v>
@@ -17452,7 +17449,7 @@
         <v>1</v>
       </c>
       <c r="K469">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="470" spans="1:11">
@@ -17472,13 +17469,13 @@
         <v>150</v>
       </c>
       <c r="F470">
-        <v>58800382.314</v>
+        <v>58962655.425</v>
       </c>
       <c r="G470">
-        <v>0.006230134991228343</v>
+        <v>0.006239032684492997</v>
       </c>
       <c r="H470" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I470">
         <v>6</v>
@@ -17487,7 +17484,7 @@
         <v>1</v>
       </c>
       <c r="K470">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="471" spans="1:11">
@@ -17510,10 +17507,10 @@
         <v>57840649.50099999</v>
       </c>
       <c r="G471">
-        <v>0.006128447472453866</v>
+        <v>0.006120309543861466</v>
       </c>
       <c r="H471" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I471">
         <v>6</v>
@@ -17522,7 +17519,7 @@
         <v>1</v>
       </c>
       <c r="K471">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="472" spans="1:11">
@@ -17542,13 +17539,13 @@
         <v>203</v>
       </c>
       <c r="F472">
-        <v>54355644.18</v>
+        <v>54486411.003</v>
       </c>
       <c r="G472">
-        <v>0.005759197261136625</v>
+        <v>0.005765386525727965</v>
       </c>
       <c r="H472" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I472">
         <v>6</v>
@@ -17557,7 +17554,7 @@
         <v>1</v>
       </c>
       <c r="K472">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="473" spans="1:11">
@@ -17577,13 +17574,13 @@
         <v>177</v>
       </c>
       <c r="F473">
-        <v>52481295.569</v>
+        <v>52483368.746</v>
       </c>
       <c r="G473">
-        <v>0.00556060255124524</v>
+        <v>0.005553438030196929</v>
       </c>
       <c r="H473" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I473">
         <v>6</v>
@@ -17592,7 +17589,7 @@
         <v>1</v>
       </c>
       <c r="K473">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="474" spans="1:11">
@@ -17612,13 +17609,13 @@
         <v>165</v>
       </c>
       <c r="F474">
-        <v>48076988.802</v>
+        <v>48076991.15</v>
       </c>
       <c r="G474">
-        <v>0.005093948685719993</v>
+        <v>0.005087184710303108</v>
       </c>
       <c r="H474" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I474">
         <v>6</v>
@@ -17627,7 +17624,7 @@
         <v>1</v>
       </c>
       <c r="K474">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="475" spans="1:11">
@@ -17650,10 +17647,10 @@
         <v>46024734.933</v>
       </c>
       <c r="G475">
-        <v>0.004876504204290211</v>
+        <v>0.004870028723644677</v>
       </c>
       <c r="H475" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I475">
         <v>6</v>
@@ -17662,7 +17659,7 @@
         <v>1</v>
       </c>
       <c r="K475">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="476" spans="1:11">
@@ -17685,10 +17682,10 @@
         <v>46010873.192</v>
       </c>
       <c r="G476">
-        <v>0.0048750354975532</v>
+        <v>0.00486856196719452</v>
       </c>
       <c r="H476" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I476">
         <v>6</v>
@@ -17697,7 +17694,7 @@
         <v>1</v>
       </c>
       <c r="K476">
-        <v>9438059110.563</v>
+        <v>9450608516.854</v>
       </c>
     </row>
     <row r="477" spans="1:11">
@@ -17717,13 +17714,13 @@
         <v>170</v>
       </c>
       <c r="F477">
-        <v>1121363817.42</v>
+        <v>1121364074.17</v>
       </c>
       <c r="G477">
-        <v>0.07637234384858292</v>
+        <v>0.07637948258790246</v>
       </c>
       <c r="H477" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I477">
         <v>6</v>
@@ -17732,7 +17729,7 @@
         <v>1</v>
       </c>
       <c r="K477">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="478" spans="1:11">
@@ -17752,13 +17749,13 @@
         <v>166</v>
       </c>
       <c r="F478">
-        <v>444209388.488</v>
+        <v>445235134.667</v>
       </c>
       <c r="G478">
-        <v>0.03025361763181251</v>
+        <v>0.03032630525549106</v>
       </c>
       <c r="H478" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I478">
         <v>6</v>
@@ -17767,7 +17764,7 @@
         <v>1</v>
       </c>
       <c r="K478">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="479" spans="1:11">
@@ -17790,10 +17787,10 @@
         <v>395514987.077</v>
       </c>
       <c r="G479">
-        <v>0.02693720460841199</v>
+        <v>0.0269397163370533</v>
       </c>
       <c r="H479" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I479">
         <v>6</v>
@@ -17802,7 +17799,7 @@
         <v>1</v>
       </c>
       <c r="K479">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="480" spans="1:11">
@@ -17822,13 +17819,13 @@
         <v>167</v>
       </c>
       <c r="F480">
-        <v>367805593.051</v>
+        <v>367756755.682</v>
       </c>
       <c r="G480">
-        <v>0.02505001034057971</v>
+        <v>0.02504901963975216</v>
       </c>
       <c r="H480" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I480">
         <v>6</v>
@@ -17837,7 +17834,7 @@
         <v>1</v>
       </c>
       <c r="K480">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="481" spans="1:11">
@@ -17860,10 +17857,10 @@
         <v>258421656.51</v>
       </c>
       <c r="G481">
-        <v>0.01760023580421091</v>
+        <v>0.01760187691794212</v>
       </c>
       <c r="H481" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I481">
         <v>6</v>
@@ -17872,7 +17869,7 @@
         <v>1</v>
       </c>
       <c r="K481">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="482" spans="1:11">
@@ -17895,10 +17892,10 @@
         <v>246199513.649</v>
       </c>
       <c r="G482">
-        <v>0.0167678264802732</v>
+        <v>0.01676938997695503</v>
       </c>
       <c r="H482" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I482">
         <v>6</v>
@@ -17907,7 +17904,7 @@
         <v>1</v>
       </c>
       <c r="K482">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="483" spans="1:11">
@@ -17927,13 +17924,13 @@
         <v>114</v>
       </c>
       <c r="F483">
-        <v>229136117.083</v>
+        <v>229132658.496</v>
       </c>
       <c r="G483">
-        <v>0.01560569553800543</v>
+        <v>0.01560691509835356</v>
       </c>
       <c r="H483" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I483">
         <v>6</v>
@@ -17942,7 +17939,7 @@
         <v>1</v>
       </c>
       <c r="K483">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="484" spans="1:11">
@@ -17965,10 +17962,10 @@
         <v>208513221.854</v>
       </c>
       <c r="G484">
-        <v>0.01420113903179834</v>
+        <v>0.01420246320066307</v>
       </c>
       <c r="H484" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I484">
         <v>6</v>
@@ -17977,7 +17974,7 @@
         <v>1</v>
       </c>
       <c r="K484">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="485" spans="1:11">
@@ -17997,13 +17994,13 @@
         <v>199</v>
       </c>
       <c r="F485">
-        <v>176331920.711</v>
+        <v>176348061.66</v>
       </c>
       <c r="G485">
-        <v>0.01200937810799509</v>
+        <v>0.0120115973172584</v>
       </c>
       <c r="H485" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I485">
         <v>6</v>
@@ -18012,7 +18009,7 @@
         <v>1</v>
       </c>
       <c r="K485">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="486" spans="1:11">
@@ -18032,13 +18029,13 @@
         <v>191</v>
       </c>
       <c r="F486">
-        <v>170866171.543</v>
+        <v>170869648.693</v>
       </c>
       <c r="G486">
-        <v>0.01163712418971813</v>
+        <v>0.01163844611912319</v>
       </c>
       <c r="H486" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I486">
         <v>6</v>
@@ -18047,7 +18044,7 @@
         <v>1</v>
       </c>
       <c r="K486">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="487" spans="1:11">
@@ -18067,13 +18064,13 @@
         <v>195</v>
       </c>
       <c r="F487">
-        <v>151554262.27</v>
+        <v>151554211.02</v>
       </c>
       <c r="G487">
-        <v>0.0103218545578126</v>
+        <v>0.0103228135164695</v>
       </c>
       <c r="H487" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I487">
         <v>6</v>
@@ -18082,7 +18079,7 @@
         <v>1</v>
       </c>
       <c r="K487">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="488" spans="1:11">
@@ -18102,13 +18099,13 @@
         <v>205</v>
       </c>
       <c r="F488">
-        <v>140337619.384</v>
+        <v>140338274.149</v>
       </c>
       <c r="G488">
-        <v>0.00955792647844288</v>
+        <v>0.009558862294312116</v>
       </c>
       <c r="H488" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I488">
         <v>6</v>
@@ -18117,7 +18114,7 @@
         <v>1</v>
       </c>
       <c r="K488">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="489" spans="1:11">
@@ -18137,13 +18134,13 @@
         <v>151</v>
       </c>
       <c r="F489">
-        <v>130483238.605</v>
+        <v>129928630.595</v>
       </c>
       <c r="G489">
-        <v>0.008886777520738664</v>
+        <v>0.00884983013705533</v>
       </c>
       <c r="H489" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I489">
         <v>6</v>
@@ -18152,7 +18149,7 @@
         <v>1</v>
       </c>
       <c r="K489">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="490" spans="1:11">
@@ -18172,13 +18169,13 @@
         <v>194</v>
       </c>
       <c r="F490">
-        <v>121409546.965</v>
+        <v>121411536.936</v>
       </c>
       <c r="G490">
-        <v>0.008268798692511016</v>
+        <v>0.008269705250043386</v>
       </c>
       <c r="H490" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I490">
         <v>6</v>
@@ -18187,7 +18184,7 @@
         <v>1</v>
       </c>
       <c r="K490">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="491" spans="1:11">
@@ -18207,13 +18204,13 @@
         <v>174</v>
       </c>
       <c r="F491">
-        <v>119645988.88</v>
+        <v>119646177.037</v>
       </c>
       <c r="G491">
-        <v>0.008148688642255916</v>
+        <v>0.008149461273289579</v>
       </c>
       <c r="H491" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I491">
         <v>6</v>
@@ -18222,7 +18219,7 @@
         <v>1</v>
       </c>
       <c r="K491">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="492" spans="1:11">
@@ -18242,13 +18239,13 @@
         <v>164</v>
       </c>
       <c r="F492">
-        <v>118881060.114</v>
+        <v>118881650.86</v>
       </c>
       <c r="G492">
-        <v>0.008096591899139098</v>
+        <v>0.008097387094020558</v>
       </c>
       <c r="H492" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I492">
         <v>6</v>
@@ -18257,7 +18254,7 @@
         <v>1</v>
       </c>
       <c r="K492">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="493" spans="1:11">
@@ -18277,13 +18274,13 @@
         <v>169</v>
       </c>
       <c r="F493">
-        <v>95162703.67399999</v>
+        <v>95157020.42299999</v>
       </c>
       <c r="G493">
-        <v>0.006481213869797463</v>
+        <v>0.006481431099792274</v>
       </c>
       <c r="H493" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I493">
         <v>6</v>
@@ -18292,7 +18289,7 @@
         <v>1</v>
       </c>
       <c r="K493">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="494" spans="1:11">
@@ -18312,13 +18309,13 @@
         <v>206</v>
       </c>
       <c r="F494">
-        <v>94965177.854</v>
+        <v>94964709.226</v>
       </c>
       <c r="G494">
-        <v>0.006467761046004092</v>
+        <v>0.006468332205275261</v>
       </c>
       <c r="H494" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I494">
         <v>6</v>
@@ -18327,7 +18324,7 @@
         <v>1</v>
       </c>
       <c r="K494">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="495" spans="1:11">
@@ -18350,10 +18347,10 @@
         <v>92560178.726</v>
       </c>
       <c r="G495">
-        <v>0.006303964588952576</v>
+        <v>0.006304552394875353</v>
       </c>
       <c r="H495" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I495">
         <v>6</v>
@@ -18362,7 +18359,7 @@
         <v>1</v>
       </c>
       <c r="K495">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="496" spans="1:11">
@@ -18382,13 +18379,13 @@
         <v>207</v>
       </c>
       <c r="F496">
-        <v>87737757.80599999</v>
+        <v>87737931.36999999</v>
       </c>
       <c r="G496">
-        <v>0.005975525608700643</v>
+        <v>0.005976094611675208</v>
       </c>
       <c r="H496" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I496">
         <v>6</v>
@@ -18397,7 +18394,7 @@
         <v>1</v>
       </c>
       <c r="K496">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="497" spans="1:11">
@@ -18417,13 +18414,13 @@
         <v>208</v>
       </c>
       <c r="F497">
-        <v>81682524.52599999</v>
+        <v>81682815.05</v>
       </c>
       <c r="G497">
-        <v>0.005563123896642964</v>
+        <v>0.005563662412192198</v>
       </c>
       <c r="H497" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I497">
         <v>6</v>
@@ -18432,7 +18429,7 @@
         <v>1</v>
       </c>
       <c r="K497">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="498" spans="1:11">
@@ -18452,13 +18449,13 @@
         <v>209</v>
       </c>
       <c r="F498">
-        <v>79081346.45</v>
+        <v>79081262.06300001</v>
       </c>
       <c r="G498">
-        <v>0.005385966346750965</v>
+        <v>0.005386462807131596</v>
       </c>
       <c r="H498" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I498">
         <v>6</v>
@@ -18467,7 +18464,7 @@
         <v>1</v>
       </c>
       <c r="K498">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="499" spans="1:11">
@@ -18490,10 +18487,10 @@
         <v>78151428.53199999</v>
       </c>
       <c r="G499">
-        <v>0.005322632743614156</v>
+        <v>0.005323129046378443</v>
       </c>
       <c r="H499" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I499">
         <v>6</v>
@@ -18502,7 +18499,7 @@
         <v>1</v>
       </c>
       <c r="K499">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="500" spans="1:11">
@@ -18522,13 +18519,13 @@
         <v>210</v>
       </c>
       <c r="F500">
-        <v>74302526.726</v>
+        <v>74326520.499</v>
       </c>
       <c r="G500">
-        <v>0.005060496898315015</v>
+        <v>0.005062603046628461</v>
       </c>
       <c r="H500" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I500">
         <v>6</v>
@@ -18537,7 +18534,7 @@
         <v>1</v>
       </c>
       <c r="K500">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="501" spans="1:11">
@@ -18557,13 +18554,13 @@
         <v>153</v>
       </c>
       <c r="F501">
-        <v>74236128.40899999</v>
+        <v>74237113.38500001</v>
       </c>
       <c r="G501">
-        <v>0.005055974730738252</v>
+        <v>0.005056513258963335</v>
       </c>
       <c r="H501" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I501">
         <v>6</v>
@@ -18572,7 +18569,7 @@
         <v>1</v>
       </c>
       <c r="K501">
-        <v>14682851944.982</v>
+        <v>14681482986.998</v>
       </c>
     </row>
     <row r="502" spans="1:11">
@@ -18592,13 +18589,13 @@
         <v>166</v>
       </c>
       <c r="F502">
-        <v>802008291.443</v>
+        <v>802023678.444</v>
       </c>
       <c r="G502">
-        <v>0.06140109708277931</v>
+        <v>0.06139496020018641</v>
       </c>
       <c r="H502" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I502">
         <v>6</v>
@@ -18607,7 +18604,7 @@
         <v>1</v>
       </c>
       <c r="K502">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="503" spans="1:11">
@@ -18627,13 +18624,13 @@
         <v>170</v>
       </c>
       <c r="F503">
-        <v>394889673.97</v>
+        <v>395674310.668</v>
       </c>
       <c r="G503">
-        <v>0.03023242959844423</v>
+        <v>0.03028889197240107</v>
       </c>
       <c r="H503" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I503">
         <v>6</v>
@@ -18642,7 +18639,7 @@
         <v>1</v>
       </c>
       <c r="K503">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="504" spans="1:11">
@@ -18665,10 +18662,10 @@
         <v>302784399.26</v>
       </c>
       <c r="G504">
-        <v>0.02318092530024122</v>
+        <v>0.0231781637393428</v>
       </c>
       <c r="H504" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I504">
         <v>6</v>
@@ -18677,7 +18674,7 @@
         <v>1</v>
       </c>
       <c r="K504">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="505" spans="1:11">
@@ -18700,10 +18697,10 @@
         <v>228793241.621</v>
       </c>
       <c r="G505">
-        <v>0.01751622294998833</v>
+        <v>0.01751413622930052</v>
       </c>
       <c r="H505" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I505">
         <v>6</v>
@@ -18712,7 +18709,7 @@
         <v>1</v>
       </c>
       <c r="K505">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="506" spans="1:11">
@@ -18732,13 +18729,13 @@
         <v>167</v>
       </c>
       <c r="F506">
-        <v>180741485.862</v>
+        <v>180738253.779</v>
       </c>
       <c r="G506">
-        <v>0.01383741993531145</v>
+        <v>0.01383552405702157</v>
       </c>
       <c r="H506" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I506">
         <v>6</v>
@@ -18747,7 +18744,7 @@
         <v>1</v>
       </c>
       <c r="K506">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="507" spans="1:11">
@@ -18767,13 +18764,13 @@
         <v>195</v>
       </c>
       <c r="F507">
-        <v>180559527.283</v>
+        <v>180559541.179</v>
       </c>
       <c r="G507">
-        <v>0.01382348933572361</v>
+        <v>0.01382184359688159</v>
       </c>
       <c r="H507" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I507">
         <v>6</v>
@@ -18782,7 +18779,7 @@
         <v>1</v>
       </c>
       <c r="K507">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="508" spans="1:11">
@@ -18802,13 +18799,13 @@
         <v>114</v>
       </c>
       <c r="F508">
-        <v>161678889.071</v>
+        <v>161754820.907</v>
       </c>
       <c r="G508">
-        <v>0.01237800315782636</v>
+        <v>0.01238234114364362</v>
       </c>
       <c r="H508" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I508">
         <v>6</v>
@@ -18817,7 +18814,7 @@
         <v>1</v>
       </c>
       <c r="K508">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="509" spans="1:11">
@@ -18840,10 +18837,10 @@
         <v>151329630.27</v>
       </c>
       <c r="G509">
-        <v>0.01158567239123082</v>
+        <v>0.01158429218144872</v>
       </c>
       <c r="H509" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I509">
         <v>6</v>
@@ -18852,7 +18849,7 @@
         <v>1</v>
       </c>
       <c r="K509">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="510" spans="1:11">
@@ -18872,13 +18869,13 @@
         <v>151</v>
       </c>
       <c r="F510">
-        <v>138463734.469</v>
+        <v>138460002.346</v>
       </c>
       <c r="G510">
-        <v>0.01060066995975625</v>
+        <v>0.01059912139981031</v>
       </c>
       <c r="H510" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I510">
         <v>6</v>
@@ -18887,7 +18884,7 @@
         <v>1</v>
       </c>
       <c r="K510">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="511" spans="1:11">
@@ -18910,10 +18907,10 @@
         <v>127263224.426</v>
       </c>
       <c r="G511">
-        <v>0.009743168096166396</v>
+        <v>0.009742007385293442</v>
       </c>
       <c r="H511" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I511">
         <v>6</v>
@@ -18922,7 +18919,7 @@
         <v>1</v>
       </c>
       <c r="K511">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="512" spans="1:11">
@@ -18942,13 +18939,13 @@
         <v>169</v>
       </c>
       <c r="F512">
-        <v>115015614.384</v>
+        <v>115016307.062</v>
       </c>
       <c r="G512">
-        <v>0.008805501115357741</v>
+        <v>0.008804505133992701</v>
       </c>
       <c r="H512" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I512">
         <v>6</v>
@@ -18957,7 +18954,7 @@
         <v>1</v>
       </c>
       <c r="K512">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="513" spans="1:11">
@@ -18977,13 +18974,13 @@
         <v>191</v>
       </c>
       <c r="F513">
-        <v>97086965.376</v>
+        <v>97097116.419</v>
       </c>
       <c r="G513">
-        <v>0.00743289845021245</v>
+        <v>0.007432790026427639</v>
       </c>
       <c r="H513" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I513">
         <v>6</v>
@@ -18992,7 +18989,7 @@
         <v>1</v>
       </c>
       <c r="K513">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="514" spans="1:11">
@@ -19012,13 +19009,13 @@
         <v>164</v>
       </c>
       <c r="F514">
-        <v>96681994.329</v>
+        <v>96686105.126</v>
       </c>
       <c r="G514">
-        <v>0.007401894198962351</v>
+        <v>0.007401327087547183</v>
       </c>
       <c r="H514" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I514">
         <v>6</v>
@@ -19027,7 +19024,7 @@
         <v>1</v>
       </c>
       <c r="K514">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="515" spans="1:11">
@@ -19047,13 +19044,13 @@
         <v>194</v>
       </c>
       <c r="F515">
-        <v>90253444.45299999</v>
+        <v>90257602.502</v>
       </c>
       <c r="G515">
-        <v>0.006909729692374056</v>
+        <v>0.006909224830026576</v>
       </c>
       <c r="H515" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I515">
         <v>6</v>
@@ -19062,7 +19059,7 @@
         <v>1</v>
       </c>
       <c r="K515">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="516" spans="1:11">
@@ -19082,13 +19079,13 @@
         <v>189</v>
       </c>
       <c r="F516">
-        <v>87252373.721</v>
+        <v>87242570.111</v>
       </c>
       <c r="G516">
-        <v>0.006679970178246994</v>
+        <v>0.006678423921496239</v>
       </c>
       <c r="H516" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I516">
         <v>6</v>
@@ -19097,7 +19094,7 @@
         <v>1</v>
       </c>
       <c r="K516">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="517" spans="1:11">
@@ -19120,10 +19117,10 @@
         <v>87150892.601</v>
       </c>
       <c r="G517">
-        <v>0.006672200866922321</v>
+        <v>0.006671406002662941</v>
       </c>
       <c r="H517" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I517">
         <v>6</v>
@@ -19132,7 +19129,7 @@
         <v>1</v>
       </c>
       <c r="K517">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="518" spans="1:11">
@@ -19152,13 +19149,13 @@
         <v>210</v>
       </c>
       <c r="F518">
-        <v>85089452.66</v>
+        <v>85123778.98800001</v>
       </c>
       <c r="G518">
-        <v>0.00651437871558281</v>
+        <v>0.0065162303352402</v>
       </c>
       <c r="H518" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I518">
         <v>6</v>
@@ -19167,7 +19164,7 @@
         <v>1</v>
       </c>
       <c r="K518">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="519" spans="1:11">
@@ -19187,13 +19184,13 @@
         <v>150</v>
       </c>
       <c r="F519">
-        <v>84839902.171</v>
+        <v>84850885.37799999</v>
       </c>
       <c r="G519">
-        <v>0.006495273334796067</v>
+        <v>0.006495340313193293</v>
       </c>
       <c r="H519" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I519">
         <v>6</v>
@@ -19202,7 +19199,7 @@
         <v>1</v>
       </c>
       <c r="K519">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="520" spans="1:11">
@@ -19222,13 +19219,13 @@
         <v>211</v>
       </c>
       <c r="F520">
-        <v>84715059.889</v>
+        <v>84720735.351</v>
       </c>
       <c r="G520">
-        <v>0.006485715512066671</v>
+        <v>0.006485377320899574</v>
       </c>
       <c r="H520" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I520">
         <v>6</v>
@@ -19237,7 +19234,7 @@
         <v>1</v>
       </c>
       <c r="K520">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="521" spans="1:11">
@@ -19260,10 +19257,10 @@
         <v>81675686.736</v>
       </c>
       <c r="G521">
-        <v>0.006253023595998857</v>
+        <v>0.006252278668640006</v>
       </c>
       <c r="H521" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I521">
         <v>6</v>
@@ -19272,7 +19269,7 @@
         <v>1</v>
       </c>
       <c r="K521">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="522" spans="1:11">
@@ -19292,13 +19289,13 @@
         <v>176</v>
       </c>
       <c r="F522">
-        <v>80053561.56400001</v>
+        <v>80061310.169</v>
       </c>
       <c r="G522">
-        <v>0.006128835023101203</v>
+        <v>0.006128698046592326</v>
       </c>
       <c r="H522" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I522">
         <v>6</v>
@@ -19307,7 +19304,7 @@
         <v>1</v>
       </c>
       <c r="K522">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="523" spans="1:11">
@@ -19327,13 +19324,13 @@
         <v>199</v>
       </c>
       <c r="F523">
-        <v>72167484.105</v>
+        <v>72181333.426</v>
       </c>
       <c r="G523">
-        <v>0.005525083400046081</v>
+        <v>0.005525485359089784</v>
       </c>
       <c r="H523" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I523">
         <v>6</v>
@@ -19342,7 +19339,7 @@
         <v>1</v>
       </c>
       <c r="K523">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="524" spans="1:11">
@@ -19362,13 +19359,13 @@
         <v>206</v>
       </c>
       <c r="F524">
-        <v>70495382.92299999</v>
+        <v>70495408.84</v>
       </c>
       <c r="G524">
-        <v>0.005397068704807098</v>
+        <v>0.005396427731939923</v>
       </c>
       <c r="H524" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I524">
         <v>6</v>
@@ -19377,7 +19374,7 @@
         <v>1</v>
       </c>
       <c r="K524">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="525" spans="1:11">
@@ -19397,13 +19394,13 @@
         <v>203</v>
       </c>
       <c r="F525">
-        <v>69567149.873</v>
+        <v>69565912.52599999</v>
       </c>
       <c r="G525">
-        <v>0.005326003943723459</v>
+        <v>0.005325274733920009</v>
       </c>
       <c r="H525" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I525">
         <v>6</v>
@@ -19412,7 +19409,7 @@
         <v>1</v>
       </c>
       <c r="K525">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="526" spans="1:11">
@@ -19432,13 +19429,13 @@
         <v>212</v>
       </c>
       <c r="F526">
-        <v>65433729.459</v>
+        <v>65439178.882</v>
       </c>
       <c r="G526">
-        <v>0.005009552666558586</v>
+        <v>0.005009373028471994</v>
       </c>
       <c r="H526" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I526">
         <v>6</v>
@@ -19447,7 +19444,7 @@
         <v>1</v>
       </c>
       <c r="K526">
-        <v>13061790905.165</v>
+        <v>13063347151.442</v>
       </c>
     </row>
     <row r="527" spans="1:11">
@@ -19467,13 +19464,13 @@
         <v>166</v>
       </c>
       <c r="F527">
-        <v>874648826.1719999</v>
+        <v>872593830.478</v>
       </c>
       <c r="G527">
-        <v>0.07268682712705327</v>
+        <v>0.07242726539945928</v>
       </c>
       <c r="H527" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I527">
         <v>6</v>
@@ -19482,7 +19479,7 @@
         <v>1</v>
       </c>
       <c r="K527">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="528" spans="1:11">
@@ -19502,13 +19499,13 @@
         <v>170</v>
       </c>
       <c r="F528">
-        <v>265993859.281</v>
+        <v>261017080.423</v>
       </c>
       <c r="G528">
-        <v>0.0221051570503265</v>
+        <v>0.0216650091913127</v>
       </c>
       <c r="H528" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I528">
         <v>6</v>
@@ -19517,7 +19514,7 @@
         <v>1</v>
       </c>
       <c r="K528">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="529" spans="1:11">
@@ -19540,10 +19537,10 @@
         <v>226615826.494</v>
       </c>
       <c r="G529">
-        <v>0.01883268451489862</v>
+        <v>0.01880962715517683</v>
       </c>
       <c r="H529" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I529">
         <v>6</v>
@@ -19552,7 +19549,7 @@
         <v>1</v>
       </c>
       <c r="K529">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="530" spans="1:11">
@@ -19575,10 +19572,10 @@
         <v>225135226.515</v>
       </c>
       <c r="G530">
-        <v>0.01870964071549297</v>
+        <v>0.01868673400158815</v>
       </c>
       <c r="H530" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I530">
         <v>6</v>
@@ -19587,7 +19584,7 @@
         <v>1</v>
       </c>
       <c r="K530">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="531" spans="1:11">
@@ -19601,19 +19598,19 @@
         <v>5</v>
       </c>
       <c r="D531" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="E531" t="s">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="F531">
-        <v>219466328.146</v>
+        <v>220952091.919</v>
       </c>
       <c r="G531">
-        <v>0.0182385325136427</v>
+        <v>0.01833952435031181</v>
       </c>
       <c r="H531" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I531">
         <v>6</v>
@@ -19622,7 +19619,7 @@
         <v>1</v>
       </c>
       <c r="K531">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="532" spans="1:11">
@@ -19636,19 +19633,19 @@
         <v>6</v>
       </c>
       <c r="D532" t="s">
-        <v>55</v>
+        <v>26</v>
       </c>
       <c r="E532" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="F532">
-        <v>218998333.366</v>
+        <v>219464536.89</v>
       </c>
       <c r="G532">
-        <v>0.01819964026951874</v>
+        <v>0.01821605391181161</v>
       </c>
       <c r="H532" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I532">
         <v>6</v>
@@ -19657,7 +19654,7 @@
         <v>1</v>
       </c>
       <c r="K532">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="533" spans="1:11">
@@ -19677,13 +19674,13 @@
         <v>137</v>
       </c>
       <c r="F533">
-        <v>157593322.531</v>
+        <v>157593957.415</v>
       </c>
       <c r="G533">
-        <v>0.01309663747143259</v>
+        <v>0.01308065560444627</v>
       </c>
       <c r="H533" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I533">
         <v>6</v>
@@ -19692,7 +19689,7 @@
         <v>1</v>
       </c>
       <c r="K533">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="534" spans="1:11">
@@ -19712,13 +19709,13 @@
         <v>213</v>
       </c>
       <c r="F534">
-        <v>157387841.303</v>
+        <v>157272951.497</v>
       </c>
       <c r="G534">
-        <v>0.01307956115685859</v>
+        <v>0.01305401138578952</v>
       </c>
       <c r="H534" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I534">
         <v>6</v>
@@ -19727,7 +19724,7 @@
         <v>1</v>
       </c>
       <c r="K534">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="535" spans="1:11">
@@ -19747,13 +19744,13 @@
         <v>160</v>
       </c>
       <c r="F535">
-        <v>156580846.191</v>
+        <v>156580865.972</v>
       </c>
       <c r="G535">
-        <v>0.01301249662485088</v>
+        <v>0.01299656671881217</v>
       </c>
       <c r="H535" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I535">
         <v>6</v>
@@ -19762,7 +19759,7 @@
         <v>1</v>
       </c>
       <c r="K535">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="536" spans="1:11">
@@ -19782,13 +19779,13 @@
         <v>203</v>
       </c>
       <c r="F536">
-        <v>143379821.495</v>
+        <v>143682560.126</v>
       </c>
       <c r="G536">
-        <v>0.01191543850133215</v>
+        <v>0.01192597810348825</v>
       </c>
       <c r="H536" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I536">
         <v>6</v>
@@ -19797,7 +19794,7 @@
         <v>1</v>
       </c>
       <c r="K536">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="537" spans="1:11">
@@ -19817,13 +19814,13 @@
         <v>114</v>
       </c>
       <c r="F537">
-        <v>135858803.405</v>
+        <v>135907960.608</v>
       </c>
       <c r="G537">
-        <v>0.01129041171873202</v>
+        <v>0.01128066872471779</v>
       </c>
       <c r="H537" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I537">
         <v>6</v>
@@ -19832,7 +19829,7 @@
         <v>1</v>
       </c>
       <c r="K537">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="538" spans="1:11">
@@ -19852,13 +19849,13 @@
         <v>174</v>
       </c>
       <c r="F538">
-        <v>130137547.449</v>
+        <v>130137523.81</v>
       </c>
       <c r="G538">
-        <v>0.01081495239130863</v>
+        <v>0.01080170939353548</v>
       </c>
       <c r="H538" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I538">
         <v>6</v>
@@ -19867,7 +19864,7 @@
         <v>1</v>
       </c>
       <c r="K538">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="539" spans="1:11">
@@ -19887,13 +19884,13 @@
         <v>169</v>
       </c>
       <c r="F539">
-        <v>109850647.066</v>
+        <v>110179394.944</v>
       </c>
       <c r="G539">
-        <v>0.009129029564959468</v>
+        <v>0.009145139468599673</v>
       </c>
       <c r="H539" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I539">
         <v>6</v>
@@ -19902,7 +19899,7 @@
         <v>1</v>
       </c>
       <c r="K539">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="540" spans="1:11">
@@ -19922,13 +19919,13 @@
         <v>195</v>
       </c>
       <c r="F540">
-        <v>102037268.569</v>
+        <v>102037324.113</v>
       </c>
       <c r="G540">
-        <v>0.008479706459393452</v>
+        <v>0.008469329138087713</v>
       </c>
       <c r="H540" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I540">
         <v>6</v>
@@ -19937,7 +19934,7 @@
         <v>1</v>
       </c>
       <c r="K540">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="541" spans="1:11">
@@ -19957,13 +19954,13 @@
         <v>164</v>
       </c>
       <c r="F541">
-        <v>93800309.649</v>
+        <v>93796126.626</v>
       </c>
       <c r="G541">
-        <v>0.007795182120990074</v>
+        <v>0.007785291070487195</v>
       </c>
       <c r="H541" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I541">
         <v>6</v>
@@ -19972,7 +19969,7 @@
         <v>1</v>
       </c>
       <c r="K541">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="542" spans="1:11">
@@ -19992,13 +19989,13 @@
         <v>150</v>
       </c>
       <c r="F542">
-        <v>92632123.491</v>
+        <v>92880517.611</v>
       </c>
       <c r="G542">
-        <v>0.007698101163721328</v>
+        <v>0.007709293447291514</v>
       </c>
       <c r="H542" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I542">
         <v>6</v>
@@ -20007,7 +20004,7 @@
         <v>1</v>
       </c>
       <c r="K542">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="543" spans="1:11">
@@ -20027,13 +20024,13 @@
         <v>157</v>
       </c>
       <c r="F543">
-        <v>84128234.25899999</v>
+        <v>82842398.04000001</v>
       </c>
       <c r="G543">
-        <v>0.006991393845289004</v>
+        <v>0.006876106774539015</v>
       </c>
       <c r="H543" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I543">
         <v>6</v>
@@ -20042,7 +20039,7 @@
         <v>1</v>
       </c>
       <c r="K543">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="544" spans="1:11">
@@ -20062,13 +20059,13 @@
         <v>118</v>
       </c>
       <c r="F544">
-        <v>81316979.427</v>
+        <v>81386580.882</v>
       </c>
       <c r="G544">
-        <v>0.006757767288127773</v>
+        <v>0.006755270651256098</v>
       </c>
       <c r="H544" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I544">
         <v>6</v>
@@ -20077,7 +20074,7 @@
         <v>1</v>
       </c>
       <c r="K544">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="545" spans="1:11">
@@ -20097,13 +20094,13 @@
         <v>102</v>
       </c>
       <c r="F545">
-        <v>72990847.45</v>
+        <v>75380359.112</v>
       </c>
       <c r="G545">
-        <v>0.006065832310866149</v>
+        <v>0.006256740633062522</v>
       </c>
       <c r="H545" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I545">
         <v>6</v>
@@ -20112,7 +20109,7 @@
         <v>1</v>
       </c>
       <c r="K545">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="546" spans="1:11">
@@ -20135,10 +20132,10 @@
         <v>69001039.458</v>
       </c>
       <c r="G546">
-        <v>0.005734263256970672</v>
+        <v>0.005727242644983526</v>
       </c>
       <c r="H546" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I546">
         <v>6</v>
@@ -20147,7 +20144,7 @@
         <v>1</v>
       </c>
       <c r="K546">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="547" spans="1:11">
@@ -20167,13 +20164,13 @@
         <v>214</v>
       </c>
       <c r="F547">
-        <v>67953672.824</v>
+        <v>66400744.759</v>
       </c>
       <c r="G547">
-        <v>0.005647222886954522</v>
+        <v>0.005511412292185692</v>
       </c>
       <c r="H547" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I547">
         <v>6</v>
@@ -20182,7 +20179,7 @@
         <v>1</v>
       </c>
       <c r="K547">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="548" spans="1:11">
@@ -20205,10 +20202,10 @@
         <v>64159600.333</v>
       </c>
       <c r="G548">
-        <v>0.005331920238613011</v>
+        <v>0.005325392225952238</v>
       </c>
       <c r="H548" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I548">
         <v>6</v>
@@ -20217,7 +20214,7 @@
         <v>1</v>
       </c>
       <c r="K548">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="549" spans="1:11">
@@ -20237,13 +20234,13 @@
         <v>209</v>
       </c>
       <c r="F549">
-        <v>59274055.612</v>
+        <v>59274045.33</v>
       </c>
       <c r="G549">
-        <v>0.004925911868246799</v>
+        <v>0.004919880089071666</v>
       </c>
       <c r="H549" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I549">
         <v>6</v>
@@ -20252,7 +20249,7 @@
         <v>1</v>
       </c>
       <c r="K549">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="550" spans="1:11">
@@ -20266,19 +20263,19 @@
         <v>24</v>
       </c>
       <c r="D550" t="s">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="E550" t="s">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="F550">
-        <v>57969998.11300001</v>
+        <v>58688696.538</v>
       </c>
       <c r="G550">
-        <v>0.004817539457334867</v>
+        <v>0.004871294812819813</v>
       </c>
       <c r="H550" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I550">
         <v>6</v>
@@ -20287,7 +20284,7 @@
         <v>1</v>
       </c>
       <c r="K550">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
     <row r="551" spans="1:11">
@@ -20301,19 +20298,19 @@
         <v>25</v>
       </c>
       <c r="D551" t="s">
-        <v>101</v>
+        <v>65</v>
       </c>
       <c r="E551" t="s">
-        <v>215</v>
+        <v>188</v>
       </c>
       <c r="F551">
-        <v>57607123.404</v>
+        <v>58008192.171</v>
       </c>
       <c r="G551">
-        <v>0.00478738311292256</v>
+        <v>0.004814811408201652</v>
       </c>
       <c r="H551" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I551">
         <v>6</v>
@@ -20322,7 +20319,7 @@
         <v>1</v>
       </c>
       <c r="K551">
-        <v>12033113299.101</v>
+        <v>12047863821.247</v>
       </c>
     </row>
   </sheetData>
